--- a/dttest/aidp-iam-sr-ar-testcases.xlsx
+++ b/dttest/aidp-iam-sr-ar-testcases.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SR_AR_TestCases" sheetId="1" r:id="Rfb784a25dc414d5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SR_AR_TestCases" sheetId="1" r:id="Rf66248eafc69443b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1746,13 +1746,13 @@
       <x:c r="AV5" s="2"/>
       <x:c r="AW5" s="2"/>
       <x:c r="AX5" s="2"/>
-      <x:c r="AY5" s="2" t="str">
+      <x:c r="AY5" s="2" t="str"/>
+      <x:c r="AZ5" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ5" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA5" s="2"/>
+      <x:c r="BA5" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB5" s="2"/>
       <x:c r="BC5" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -1768,7 +1768,9 @@
       <x:c r="BL5" s="2"/>
       <x:c r="BM5" s="2"/>
       <x:c r="BN5" s="2"/>
-      <x:c r="BO5" s="2"/>
+      <x:c r="BO5" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP5" s="2"/>
       <x:c r="BQ5" s="2"/>
       <x:c r="BR5" s="2" t="n">
@@ -1827,7 +1829,7 @@
       <x:c r="CT5" s="2"/>
       <x:c r="CU5" s="2"/>
       <x:c r="CV5" s="2"/>
-      <x:c r="CW5" s="2" t="str"/>
+      <x:c r="CW5" s="2"/>
       <x:c r="CX5" s="2"/>
       <x:c r="CY5" s="2"/>
       <x:c r="CZ5" s="2"/>
@@ -2032,13 +2034,13 @@
       <x:c r="AV6" s="2"/>
       <x:c r="AW6" s="2"/>
       <x:c r="AX6" s="2"/>
-      <x:c r="AY6" s="2" t="str">
+      <x:c r="AY6" s="2" t="str"/>
+      <x:c r="AZ6" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ6" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA6" s="2"/>
+      <x:c r="BA6" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB6" s="2"/>
       <x:c r="BC6" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -2054,7 +2056,9 @@
       <x:c r="BL6" s="2"/>
       <x:c r="BM6" s="2"/>
       <x:c r="BN6" s="2"/>
-      <x:c r="BO6" s="2"/>
+      <x:c r="BO6" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP6" s="2"/>
       <x:c r="BQ6" s="2"/>
       <x:c r="BR6" s="2" t="n">
@@ -2111,7 +2115,7 @@
       <x:c r="CT6" s="2"/>
       <x:c r="CU6" s="2"/>
       <x:c r="CV6" s="2"/>
-      <x:c r="CW6" s="2" t="str"/>
+      <x:c r="CW6" s="2"/>
       <x:c r="CX6" s="2"/>
       <x:c r="CY6" s="2"/>
       <x:c r="CZ6" s="2"/>
@@ -2316,13 +2320,13 @@
       <x:c r="AV7" s="2"/>
       <x:c r="AW7" s="2"/>
       <x:c r="AX7" s="2"/>
-      <x:c r="AY7" s="2" t="str">
+      <x:c r="AY7" s="2" t="str"/>
+      <x:c r="AZ7" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ7" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA7" s="2"/>
+      <x:c r="BA7" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB7" s="2"/>
       <x:c r="BC7" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -2338,7 +2342,9 @@
       <x:c r="BL7" s="2"/>
       <x:c r="BM7" s="2"/>
       <x:c r="BN7" s="2"/>
-      <x:c r="BO7" s="2"/>
+      <x:c r="BO7" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP7" s="2"/>
       <x:c r="BQ7" s="2"/>
       <x:c r="BR7" s="2" t="n">
@@ -2394,7 +2400,7 @@
       <x:c r="CT7" s="2"/>
       <x:c r="CU7" s="2"/>
       <x:c r="CV7" s="2"/>
-      <x:c r="CW7" s="2" t="str"/>
+      <x:c r="CW7" s="2"/>
       <x:c r="CX7" s="2"/>
       <x:c r="CY7" s="2"/>
       <x:c r="CZ7" s="2"/>
@@ -2599,13 +2605,13 @@
       <x:c r="AV8" s="2"/>
       <x:c r="AW8" s="2"/>
       <x:c r="AX8" s="2"/>
-      <x:c r="AY8" s="2" t="str">
+      <x:c r="AY8" s="2" t="str"/>
+      <x:c r="AZ8" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ8" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA8" s="2"/>
+      <x:c r="BA8" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB8" s="2"/>
       <x:c r="BC8" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -2621,7 +2627,9 @@
       <x:c r="BL8" s="2"/>
       <x:c r="BM8" s="2"/>
       <x:c r="BN8" s="2"/>
-      <x:c r="BO8" s="2"/>
+      <x:c r="BO8" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP8" s="2"/>
       <x:c r="BQ8" s="2"/>
       <x:c r="BR8" s="2" t="n">
@@ -2677,7 +2685,7 @@
       <x:c r="CT8" s="2"/>
       <x:c r="CU8" s="2"/>
       <x:c r="CV8" s="2"/>
-      <x:c r="CW8" s="2" t="str"/>
+      <x:c r="CW8" s="2"/>
       <x:c r="CX8" s="2"/>
       <x:c r="CY8" s="2"/>
       <x:c r="CZ8" s="2"/>
@@ -2882,13 +2890,13 @@
       <x:c r="AV9" s="2"/>
       <x:c r="AW9" s="2"/>
       <x:c r="AX9" s="2"/>
-      <x:c r="AY9" s="2" t="str">
+      <x:c r="AY9" s="2" t="str"/>
+      <x:c r="AZ9" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ9" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA9" s="2"/>
+      <x:c r="BA9" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB9" s="2"/>
       <x:c r="BC9" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -2904,7 +2912,9 @@
       <x:c r="BL9" s="2"/>
       <x:c r="BM9" s="2"/>
       <x:c r="BN9" s="2"/>
-      <x:c r="BO9" s="2"/>
+      <x:c r="BO9" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP9" s="2"/>
       <x:c r="BQ9" s="2"/>
       <x:c r="BR9" s="2" t="n">
@@ -2960,7 +2970,7 @@
       <x:c r="CT9" s="2"/>
       <x:c r="CU9" s="2"/>
       <x:c r="CV9" s="2"/>
-      <x:c r="CW9" s="2" t="str"/>
+      <x:c r="CW9" s="2"/>
       <x:c r="CX9" s="2"/>
       <x:c r="CY9" s="2"/>
       <x:c r="CZ9" s="2"/>
@@ -3165,13 +3175,13 @@
       <x:c r="AV10" s="2"/>
       <x:c r="AW10" s="2"/>
       <x:c r="AX10" s="2"/>
-      <x:c r="AY10" s="2" t="str">
+      <x:c r="AY10" s="2" t="str"/>
+      <x:c r="AZ10" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ10" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA10" s="2"/>
+      <x:c r="BA10" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB10" s="2"/>
       <x:c r="BC10" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -3187,7 +3197,9 @@
       <x:c r="BL10" s="2"/>
       <x:c r="BM10" s="2"/>
       <x:c r="BN10" s="2"/>
-      <x:c r="BO10" s="2"/>
+      <x:c r="BO10" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP10" s="2"/>
       <x:c r="BQ10" s="2"/>
       <x:c r="BR10" s="2" t="n">
@@ -3246,7 +3258,7 @@
       <x:c r="CT10" s="2"/>
       <x:c r="CU10" s="2"/>
       <x:c r="CV10" s="2"/>
-      <x:c r="CW10" s="2" t="str"/>
+      <x:c r="CW10" s="2"/>
       <x:c r="CX10" s="2"/>
       <x:c r="CY10" s="2"/>
       <x:c r="CZ10" s="2"/>
@@ -3451,13 +3463,13 @@
       <x:c r="AV11" s="2"/>
       <x:c r="AW11" s="2"/>
       <x:c r="AX11" s="2"/>
-      <x:c r="AY11" s="2" t="str">
+      <x:c r="AY11" s="2" t="str"/>
+      <x:c r="AZ11" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ11" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA11" s="2"/>
+      <x:c r="BA11" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB11" s="2"/>
       <x:c r="BC11" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -3473,7 +3485,9 @@
       <x:c r="BL11" s="2"/>
       <x:c r="BM11" s="2"/>
       <x:c r="BN11" s="2"/>
-      <x:c r="BO11" s="2"/>
+      <x:c r="BO11" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP11" s="2"/>
       <x:c r="BQ11" s="2"/>
       <x:c r="BR11" s="2" t="n">
@@ -3530,7 +3544,7 @@
       <x:c r="CT11" s="2"/>
       <x:c r="CU11" s="2"/>
       <x:c r="CV11" s="2"/>
-      <x:c r="CW11" s="2" t="str"/>
+      <x:c r="CW11" s="2"/>
       <x:c r="CX11" s="2"/>
       <x:c r="CY11" s="2"/>
       <x:c r="CZ11" s="2"/>
@@ -3735,13 +3749,13 @@
       <x:c r="AV12" s="2"/>
       <x:c r="AW12" s="2"/>
       <x:c r="AX12" s="2"/>
-      <x:c r="AY12" s="2" t="str">
+      <x:c r="AY12" s="2" t="str"/>
+      <x:c r="AZ12" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ12" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA12" s="2"/>
+      <x:c r="BA12" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB12" s="2"/>
       <x:c r="BC12" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -3757,7 +3771,9 @@
       <x:c r="BL12" s="2"/>
       <x:c r="BM12" s="2"/>
       <x:c r="BN12" s="2"/>
-      <x:c r="BO12" s="2"/>
+      <x:c r="BO12" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP12" s="2"/>
       <x:c r="BQ12" s="2"/>
       <x:c r="BR12" s="2" t="n">
@@ -3815,7 +3831,7 @@
       <x:c r="CT12" s="2"/>
       <x:c r="CU12" s="2"/>
       <x:c r="CV12" s="2"/>
-      <x:c r="CW12" s="2" t="str"/>
+      <x:c r="CW12" s="2"/>
       <x:c r="CX12" s="2"/>
       <x:c r="CY12" s="2"/>
       <x:c r="CZ12" s="2"/>
@@ -4020,13 +4036,13 @@
       <x:c r="AV13" s="2"/>
       <x:c r="AW13" s="2"/>
       <x:c r="AX13" s="2"/>
-      <x:c r="AY13" s="2" t="str">
+      <x:c r="AY13" s="2" t="str"/>
+      <x:c r="AZ13" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ13" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA13" s="2"/>
+      <x:c r="BA13" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB13" s="2"/>
       <x:c r="BC13" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -4042,7 +4058,9 @@
       <x:c r="BL13" s="2"/>
       <x:c r="BM13" s="2"/>
       <x:c r="BN13" s="2"/>
-      <x:c r="BO13" s="2"/>
+      <x:c r="BO13" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP13" s="2"/>
       <x:c r="BQ13" s="2"/>
       <x:c r="BR13" s="2" t="n">
@@ -4099,7 +4117,7 @@
       <x:c r="CT13" s="2"/>
       <x:c r="CU13" s="2"/>
       <x:c r="CV13" s="2"/>
-      <x:c r="CW13" s="2" t="str"/>
+      <x:c r="CW13" s="2"/>
       <x:c r="CX13" s="2"/>
       <x:c r="CY13" s="2"/>
       <x:c r="CZ13" s="2"/>
@@ -4304,13 +4322,13 @@
       <x:c r="AV14" s="2"/>
       <x:c r="AW14" s="2"/>
       <x:c r="AX14" s="2"/>
-      <x:c r="AY14" s="2" t="str">
+      <x:c r="AY14" s="2" t="str"/>
+      <x:c r="AZ14" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ14" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA14" s="2"/>
+      <x:c r="BA14" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB14" s="2"/>
       <x:c r="BC14" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -4326,7 +4344,9 @@
       <x:c r="BL14" s="2"/>
       <x:c r="BM14" s="2"/>
       <x:c r="BN14" s="2"/>
-      <x:c r="BO14" s="2"/>
+      <x:c r="BO14" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP14" s="2"/>
       <x:c r="BQ14" s="2"/>
       <x:c r="BR14" s="2" t="n">
@@ -4384,7 +4404,7 @@
       <x:c r="CT14" s="2"/>
       <x:c r="CU14" s="2"/>
       <x:c r="CV14" s="2"/>
-      <x:c r="CW14" s="2" t="str"/>
+      <x:c r="CW14" s="2"/>
       <x:c r="CX14" s="2"/>
       <x:c r="CY14" s="2"/>
       <x:c r="CZ14" s="2"/>
@@ -4589,13 +4609,13 @@
       <x:c r="AV15" s="2"/>
       <x:c r="AW15" s="2"/>
       <x:c r="AX15" s="2"/>
-      <x:c r="AY15" s="2" t="str">
+      <x:c r="AY15" s="2" t="str"/>
+      <x:c r="AZ15" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ15" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA15" s="2"/>
+      <x:c r="BA15" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB15" s="2"/>
       <x:c r="BC15" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -4611,7 +4631,9 @@
       <x:c r="BL15" s="2"/>
       <x:c r="BM15" s="2"/>
       <x:c r="BN15" s="2"/>
-      <x:c r="BO15" s="2"/>
+      <x:c r="BO15" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP15" s="2"/>
       <x:c r="BQ15" s="2"/>
       <x:c r="BR15" s="2" t="n">
@@ -4669,7 +4691,7 @@
       <x:c r="CT15" s="2"/>
       <x:c r="CU15" s="2"/>
       <x:c r="CV15" s="2"/>
-      <x:c r="CW15" s="2" t="str"/>
+      <x:c r="CW15" s="2"/>
       <x:c r="CX15" s="2"/>
       <x:c r="CY15" s="2"/>
       <x:c r="CZ15" s="2"/>
@@ -4874,13 +4896,13 @@
       <x:c r="AV16" s="2"/>
       <x:c r="AW16" s="2"/>
       <x:c r="AX16" s="2"/>
-      <x:c r="AY16" s="2" t="str">
+      <x:c r="AY16" s="2" t="str"/>
+      <x:c r="AZ16" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ16" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA16" s="2"/>
+      <x:c r="BA16" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB16" s="2"/>
       <x:c r="BC16" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -4896,7 +4918,9 @@
       <x:c r="BL16" s="2"/>
       <x:c r="BM16" s="2"/>
       <x:c r="BN16" s="2"/>
-      <x:c r="BO16" s="2"/>
+      <x:c r="BO16" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP16" s="2"/>
       <x:c r="BQ16" s="2"/>
       <x:c r="BR16" s="2" t="n">
@@ -4954,7 +4978,7 @@
       <x:c r="CT16" s="2"/>
       <x:c r="CU16" s="2"/>
       <x:c r="CV16" s="2"/>
-      <x:c r="CW16" s="2" t="str"/>
+      <x:c r="CW16" s="2"/>
       <x:c r="CX16" s="2"/>
       <x:c r="CY16" s="2"/>
       <x:c r="CZ16" s="2"/>
@@ -5159,13 +5183,13 @@
       <x:c r="AV17" s="2"/>
       <x:c r="AW17" s="2"/>
       <x:c r="AX17" s="2"/>
-      <x:c r="AY17" s="2" t="str">
+      <x:c r="AY17" s="2" t="str"/>
+      <x:c r="AZ17" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ17" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA17" s="2"/>
+      <x:c r="BA17" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB17" s="2"/>
       <x:c r="BC17" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -5181,7 +5205,9 @@
       <x:c r="BL17" s="2"/>
       <x:c r="BM17" s="2"/>
       <x:c r="BN17" s="2"/>
-      <x:c r="BO17" s="2"/>
+      <x:c r="BO17" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP17" s="2"/>
       <x:c r="BQ17" s="2"/>
       <x:c r="BR17" s="2" t="n">
@@ -5239,7 +5265,7 @@
       <x:c r="CT17" s="2"/>
       <x:c r="CU17" s="2"/>
       <x:c r="CV17" s="2"/>
-      <x:c r="CW17" s="2" t="str"/>
+      <x:c r="CW17" s="2"/>
       <x:c r="CX17" s="2"/>
       <x:c r="CY17" s="2"/>
       <x:c r="CZ17" s="2"/>
@@ -5444,13 +5470,13 @@
       <x:c r="AV18" s="2"/>
       <x:c r="AW18" s="2"/>
       <x:c r="AX18" s="2"/>
-      <x:c r="AY18" s="2" t="str">
+      <x:c r="AY18" s="2" t="str"/>
+      <x:c r="AZ18" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ18" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA18" s="2"/>
+      <x:c r="BA18" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB18" s="2"/>
       <x:c r="BC18" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -5466,7 +5492,9 @@
       <x:c r="BL18" s="2"/>
       <x:c r="BM18" s="2"/>
       <x:c r="BN18" s="2"/>
-      <x:c r="BO18" s="2"/>
+      <x:c r="BO18" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP18" s="2"/>
       <x:c r="BQ18" s="2"/>
       <x:c r="BR18" s="2" t="n">
@@ -5522,7 +5550,7 @@
       <x:c r="CT18" s="2"/>
       <x:c r="CU18" s="2"/>
       <x:c r="CV18" s="2"/>
-      <x:c r="CW18" s="2" t="str"/>
+      <x:c r="CW18" s="2"/>
       <x:c r="CX18" s="2"/>
       <x:c r="CY18" s="2"/>
       <x:c r="CZ18" s="2"/>
@@ -5727,13 +5755,13 @@
       <x:c r="AV19" s="2"/>
       <x:c r="AW19" s="2"/>
       <x:c r="AX19" s="2"/>
-      <x:c r="AY19" s="2" t="str">
+      <x:c r="AY19" s="2" t="str"/>
+      <x:c r="AZ19" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ19" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA19" s="2"/>
+      <x:c r="BA19" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB19" s="2"/>
       <x:c r="BC19" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -5749,7 +5777,9 @@
       <x:c r="BL19" s="2"/>
       <x:c r="BM19" s="2"/>
       <x:c r="BN19" s="2"/>
-      <x:c r="BO19" s="2"/>
+      <x:c r="BO19" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP19" s="2"/>
       <x:c r="BQ19" s="2"/>
       <x:c r="BR19" s="2" t="n">
@@ -5807,7 +5837,7 @@
       <x:c r="CT19" s="2"/>
       <x:c r="CU19" s="2"/>
       <x:c r="CV19" s="2"/>
-      <x:c r="CW19" s="2" t="str"/>
+      <x:c r="CW19" s="2"/>
       <x:c r="CX19" s="2"/>
       <x:c r="CY19" s="2"/>
       <x:c r="CZ19" s="2"/>
@@ -6506,13 +6536,13 @@
       <x:c r="AV22" s="2"/>
       <x:c r="AW22" s="2"/>
       <x:c r="AX22" s="2"/>
-      <x:c r="AY22" s="2" t="str">
+      <x:c r="AY22" s="2" t="str"/>
+      <x:c r="AZ22" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ22" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA22" s="2"/>
+      <x:c r="BA22" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB22" s="2"/>
       <x:c r="BC22" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -6528,7 +6558,9 @@
       <x:c r="BL22" s="2"/>
       <x:c r="BM22" s="2"/>
       <x:c r="BN22" s="2"/>
-      <x:c r="BO22" s="2"/>
+      <x:c r="BO22" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP22" s="2"/>
       <x:c r="BQ22" s="2"/>
       <x:c r="BR22" s="2" t="n">
@@ -6585,7 +6617,7 @@
       <x:c r="CT22" s="2"/>
       <x:c r="CU22" s="2"/>
       <x:c r="CV22" s="2"/>
-      <x:c r="CW22" s="2" t="str"/>
+      <x:c r="CW22" s="2"/>
       <x:c r="CX22" s="2"/>
       <x:c r="CY22" s="2"/>
       <x:c r="CZ22" s="2"/>
@@ -6790,13 +6822,13 @@
       <x:c r="AV23" s="2"/>
       <x:c r="AW23" s="2"/>
       <x:c r="AX23" s="2"/>
-      <x:c r="AY23" s="2" t="str">
+      <x:c r="AY23" s="2" t="str"/>
+      <x:c r="AZ23" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ23" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA23" s="2"/>
+      <x:c r="BA23" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB23" s="2"/>
       <x:c r="BC23" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -6812,7 +6844,9 @@
       <x:c r="BL23" s="2"/>
       <x:c r="BM23" s="2"/>
       <x:c r="BN23" s="2"/>
-      <x:c r="BO23" s="2"/>
+      <x:c r="BO23" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP23" s="2"/>
       <x:c r="BQ23" s="2"/>
       <x:c r="BR23" s="2" t="n">
@@ -6867,7 +6901,7 @@
       <x:c r="CT23" s="2"/>
       <x:c r="CU23" s="2"/>
       <x:c r="CV23" s="2"/>
-      <x:c r="CW23" s="2" t="str"/>
+      <x:c r="CW23" s="2"/>
       <x:c r="CX23" s="2"/>
       <x:c r="CY23" s="2"/>
       <x:c r="CZ23" s="2"/>
@@ -7072,13 +7106,13 @@
       <x:c r="AV24" s="2"/>
       <x:c r="AW24" s="2"/>
       <x:c r="AX24" s="2"/>
-      <x:c r="AY24" s="2" t="str">
+      <x:c r="AY24" s="2" t="str"/>
+      <x:c r="AZ24" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ24" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA24" s="2"/>
+      <x:c r="BA24" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB24" s="2"/>
       <x:c r="BC24" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -7094,7 +7128,9 @@
       <x:c r="BL24" s="2"/>
       <x:c r="BM24" s="2"/>
       <x:c r="BN24" s="2"/>
-      <x:c r="BO24" s="2"/>
+      <x:c r="BO24" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP24" s="2"/>
       <x:c r="BQ24" s="2"/>
       <x:c r="BR24" s="2" t="n">
@@ -7150,7 +7186,7 @@
       <x:c r="CT24" s="2"/>
       <x:c r="CU24" s="2"/>
       <x:c r="CV24" s="2"/>
-      <x:c r="CW24" s="2" t="str"/>
+      <x:c r="CW24" s="2"/>
       <x:c r="CX24" s="2"/>
       <x:c r="CY24" s="2"/>
       <x:c r="CZ24" s="2"/>
@@ -7355,13 +7391,13 @@
       <x:c r="AV25" s="2"/>
       <x:c r="AW25" s="2"/>
       <x:c r="AX25" s="2"/>
-      <x:c r="AY25" s="2" t="str">
+      <x:c r="AY25" s="2" t="str"/>
+      <x:c r="AZ25" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ25" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA25" s="2"/>
+      <x:c r="BA25" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB25" s="2"/>
       <x:c r="BC25" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -7377,7 +7413,9 @@
       <x:c r="BL25" s="2"/>
       <x:c r="BM25" s="2"/>
       <x:c r="BN25" s="2"/>
-      <x:c r="BO25" s="2"/>
+      <x:c r="BO25" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP25" s="2"/>
       <x:c r="BQ25" s="2"/>
       <x:c r="BR25" s="2" t="n">
@@ -7435,7 +7473,7 @@
       <x:c r="CT25" s="2"/>
       <x:c r="CU25" s="2"/>
       <x:c r="CV25" s="2"/>
-      <x:c r="CW25" s="2" t="str"/>
+      <x:c r="CW25" s="2"/>
       <x:c r="CX25" s="2"/>
       <x:c r="CY25" s="2"/>
       <x:c r="CZ25" s="2"/>
@@ -7640,13 +7678,13 @@
       <x:c r="AV26" s="2"/>
       <x:c r="AW26" s="2"/>
       <x:c r="AX26" s="2"/>
-      <x:c r="AY26" s="2" t="str">
+      <x:c r="AY26" s="2" t="str"/>
+      <x:c r="AZ26" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ26" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA26" s="2"/>
+      <x:c r="BA26" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB26" s="2"/>
       <x:c r="BC26" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -7662,7 +7700,9 @@
       <x:c r="BL26" s="2"/>
       <x:c r="BM26" s="2"/>
       <x:c r="BN26" s="2"/>
-      <x:c r="BO26" s="2"/>
+      <x:c r="BO26" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP26" s="2"/>
       <x:c r="BQ26" s="2"/>
       <x:c r="BR26" s="2" t="n">
@@ -7719,7 +7759,7 @@
       <x:c r="CT26" s="2"/>
       <x:c r="CU26" s="2"/>
       <x:c r="CV26" s="2"/>
-      <x:c r="CW26" s="2" t="str"/>
+      <x:c r="CW26" s="2"/>
       <x:c r="CX26" s="2"/>
       <x:c r="CY26" s="2"/>
       <x:c r="CZ26" s="2"/>
@@ -7924,13 +7964,13 @@
       <x:c r="AV27" s="2"/>
       <x:c r="AW27" s="2"/>
       <x:c r="AX27" s="2"/>
-      <x:c r="AY27" s="2" t="str">
+      <x:c r="AY27" s="2" t="str"/>
+      <x:c r="AZ27" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ27" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA27" s="2"/>
+      <x:c r="BA27" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB27" s="2"/>
       <x:c r="BC27" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -7946,7 +7986,9 @@
       <x:c r="BL27" s="2"/>
       <x:c r="BM27" s="2"/>
       <x:c r="BN27" s="2"/>
-      <x:c r="BO27" s="2"/>
+      <x:c r="BO27" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP27" s="2"/>
       <x:c r="BQ27" s="2"/>
       <x:c r="BR27" s="2" t="n">
@@ -8003,7 +8045,7 @@
       <x:c r="CT27" s="2"/>
       <x:c r="CU27" s="2"/>
       <x:c r="CV27" s="2"/>
-      <x:c r="CW27" s="2" t="str"/>
+      <x:c r="CW27" s="2"/>
       <x:c r="CX27" s="2"/>
       <x:c r="CY27" s="2"/>
       <x:c r="CZ27" s="2"/>
@@ -8208,13 +8250,13 @@
       <x:c r="AV28" s="2"/>
       <x:c r="AW28" s="2"/>
       <x:c r="AX28" s="2"/>
-      <x:c r="AY28" s="2" t="str">
+      <x:c r="AY28" s="2" t="str"/>
+      <x:c r="AZ28" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ28" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA28" s="2"/>
+      <x:c r="BA28" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB28" s="2"/>
       <x:c r="BC28" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -8230,7 +8272,9 @@
       <x:c r="BL28" s="2"/>
       <x:c r="BM28" s="2"/>
       <x:c r="BN28" s="2"/>
-      <x:c r="BO28" s="2"/>
+      <x:c r="BO28" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP28" s="2"/>
       <x:c r="BQ28" s="2"/>
       <x:c r="BR28" s="2" t="n">
@@ -8288,7 +8332,7 @@
       <x:c r="CT28" s="2"/>
       <x:c r="CU28" s="2"/>
       <x:c r="CV28" s="2"/>
-      <x:c r="CW28" s="2" t="str"/>
+      <x:c r="CW28" s="2"/>
       <x:c r="CX28" s="2"/>
       <x:c r="CY28" s="2"/>
       <x:c r="CZ28" s="2"/>
@@ -8493,13 +8537,13 @@
       <x:c r="AV29" s="2"/>
       <x:c r="AW29" s="2"/>
       <x:c r="AX29" s="2"/>
-      <x:c r="AY29" s="2" t="str">
+      <x:c r="AY29" s="2" t="str"/>
+      <x:c r="AZ29" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ29" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA29" s="2"/>
+      <x:c r="BA29" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB29" s="2"/>
       <x:c r="BC29" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -8515,7 +8559,9 @@
       <x:c r="BL29" s="2"/>
       <x:c r="BM29" s="2"/>
       <x:c r="BN29" s="2"/>
-      <x:c r="BO29" s="2"/>
+      <x:c r="BO29" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP29" s="2"/>
       <x:c r="BQ29" s="2"/>
       <x:c r="BR29" s="2" t="n">
@@ -8572,7 +8618,7 @@
       <x:c r="CT29" s="2"/>
       <x:c r="CU29" s="2"/>
       <x:c r="CV29" s="2"/>
-      <x:c r="CW29" s="2" t="str"/>
+      <x:c r="CW29" s="2"/>
       <x:c r="CX29" s="2"/>
       <x:c r="CY29" s="2"/>
       <x:c r="CZ29" s="2"/>
@@ -9271,13 +9317,13 @@
       <x:c r="AV32" s="2"/>
       <x:c r="AW32" s="2"/>
       <x:c r="AX32" s="2"/>
-      <x:c r="AY32" s="2" t="str">
+      <x:c r="AY32" s="2" t="str"/>
+      <x:c r="AZ32" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ32" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA32" s="2"/>
+      <x:c r="BA32" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB32" s="2"/>
       <x:c r="BC32" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -9293,7 +9339,9 @@
       <x:c r="BL32" s="2"/>
       <x:c r="BM32" s="2"/>
       <x:c r="BN32" s="2"/>
-      <x:c r="BO32" s="2"/>
+      <x:c r="BO32" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP32" s="2"/>
       <x:c r="BQ32" s="2"/>
       <x:c r="BR32" s="2" t="n">
@@ -9348,7 +9396,7 @@
       <x:c r="CT32" s="2"/>
       <x:c r="CU32" s="2"/>
       <x:c r="CV32" s="2"/>
-      <x:c r="CW32" s="2" t="str"/>
+      <x:c r="CW32" s="2"/>
       <x:c r="CX32" s="2"/>
       <x:c r="CY32" s="2"/>
       <x:c r="CZ32" s="2"/>
@@ -9553,13 +9601,13 @@
       <x:c r="AV33" s="2"/>
       <x:c r="AW33" s="2"/>
       <x:c r="AX33" s="2"/>
-      <x:c r="AY33" s="2" t="str">
+      <x:c r="AY33" s="2" t="str"/>
+      <x:c r="AZ33" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ33" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA33" s="2"/>
+      <x:c r="BA33" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB33" s="2"/>
       <x:c r="BC33" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -9575,7 +9623,9 @@
       <x:c r="BL33" s="2"/>
       <x:c r="BM33" s="2"/>
       <x:c r="BN33" s="2"/>
-      <x:c r="BO33" s="2"/>
+      <x:c r="BO33" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP33" s="2"/>
       <x:c r="BQ33" s="2"/>
       <x:c r="BR33" s="2" t="n">
@@ -9631,7 +9681,7 @@
       <x:c r="CT33" s="2"/>
       <x:c r="CU33" s="2"/>
       <x:c r="CV33" s="2"/>
-      <x:c r="CW33" s="2" t="str"/>
+      <x:c r="CW33" s="2"/>
       <x:c r="CX33" s="2"/>
       <x:c r="CY33" s="2"/>
       <x:c r="CZ33" s="2"/>
@@ -9836,13 +9886,13 @@
       <x:c r="AV34" s="2"/>
       <x:c r="AW34" s="2"/>
       <x:c r="AX34" s="2"/>
-      <x:c r="AY34" s="2" t="str">
+      <x:c r="AY34" s="2" t="str"/>
+      <x:c r="AZ34" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ34" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA34" s="2"/>
+      <x:c r="BA34" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB34" s="2"/>
       <x:c r="BC34" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -9858,7 +9908,9 @@
       <x:c r="BL34" s="2"/>
       <x:c r="BM34" s="2"/>
       <x:c r="BN34" s="2"/>
-      <x:c r="BO34" s="2"/>
+      <x:c r="BO34" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP34" s="2"/>
       <x:c r="BQ34" s="2"/>
       <x:c r="BR34" s="2" t="n">
@@ -9913,7 +9965,7 @@
       <x:c r="CT34" s="2"/>
       <x:c r="CU34" s="2"/>
       <x:c r="CV34" s="2"/>
-      <x:c r="CW34" s="2" t="str"/>
+      <x:c r="CW34" s="2"/>
       <x:c r="CX34" s="2"/>
       <x:c r="CY34" s="2"/>
       <x:c r="CZ34" s="2"/>
@@ -10118,13 +10170,13 @@
       <x:c r="AV35" s="2"/>
       <x:c r="AW35" s="2"/>
       <x:c r="AX35" s="2"/>
-      <x:c r="AY35" s="2" t="str">
+      <x:c r="AY35" s="2" t="str"/>
+      <x:c r="AZ35" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ35" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA35" s="2"/>
+      <x:c r="BA35" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB35" s="2"/>
       <x:c r="BC35" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -10140,7 +10192,9 @@
       <x:c r="BL35" s="2"/>
       <x:c r="BM35" s="2"/>
       <x:c r="BN35" s="2"/>
-      <x:c r="BO35" s="2"/>
+      <x:c r="BO35" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP35" s="2"/>
       <x:c r="BQ35" s="2"/>
       <x:c r="BR35" s="2" t="n">
@@ -10195,7 +10249,7 @@
       <x:c r="CT35" s="2"/>
       <x:c r="CU35" s="2"/>
       <x:c r="CV35" s="2"/>
-      <x:c r="CW35" s="2" t="str"/>
+      <x:c r="CW35" s="2"/>
       <x:c r="CX35" s="2"/>
       <x:c r="CY35" s="2"/>
       <x:c r="CZ35" s="2"/>
@@ -10400,13 +10454,13 @@
       <x:c r="AV36" s="2"/>
       <x:c r="AW36" s="2"/>
       <x:c r="AX36" s="2"/>
-      <x:c r="AY36" s="2" t="str">
+      <x:c r="AY36" s="2" t="str"/>
+      <x:c r="AZ36" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ36" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA36" s="2"/>
+      <x:c r="BA36" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB36" s="2"/>
       <x:c r="BC36" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -10422,7 +10476,9 @@
       <x:c r="BL36" s="2"/>
       <x:c r="BM36" s="2"/>
       <x:c r="BN36" s="2"/>
-      <x:c r="BO36" s="2"/>
+      <x:c r="BO36" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP36" s="2"/>
       <x:c r="BQ36" s="2"/>
       <x:c r="BR36" s="2" t="n">
@@ -10477,7 +10533,7 @@
       <x:c r="CT36" s="2"/>
       <x:c r="CU36" s="2"/>
       <x:c r="CV36" s="2"/>
-      <x:c r="CW36" s="2" t="str"/>
+      <x:c r="CW36" s="2"/>
       <x:c r="CX36" s="2"/>
       <x:c r="CY36" s="2"/>
       <x:c r="CZ36" s="2"/>
@@ -10682,13 +10738,13 @@
       <x:c r="AV37" s="2"/>
       <x:c r="AW37" s="2"/>
       <x:c r="AX37" s="2"/>
-      <x:c r="AY37" s="2" t="str">
+      <x:c r="AY37" s="2" t="str"/>
+      <x:c r="AZ37" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ37" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA37" s="2"/>
+      <x:c r="BA37" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB37" s="2"/>
       <x:c r="BC37" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -10704,7 +10760,9 @@
       <x:c r="BL37" s="2"/>
       <x:c r="BM37" s="2"/>
       <x:c r="BN37" s="2"/>
-      <x:c r="BO37" s="2"/>
+      <x:c r="BO37" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP37" s="2"/>
       <x:c r="BQ37" s="2"/>
       <x:c r="BR37" s="2" t="n">
@@ -10760,7 +10818,7 @@
       <x:c r="CT37" s="2"/>
       <x:c r="CU37" s="2"/>
       <x:c r="CV37" s="2"/>
-      <x:c r="CW37" s="2" t="str"/>
+      <x:c r="CW37" s="2"/>
       <x:c r="CX37" s="2"/>
       <x:c r="CY37" s="2"/>
       <x:c r="CZ37" s="2"/>
@@ -10965,13 +11023,13 @@
       <x:c r="AV38" s="2"/>
       <x:c r="AW38" s="2"/>
       <x:c r="AX38" s="2"/>
-      <x:c r="AY38" s="2" t="str">
+      <x:c r="AY38" s="2" t="str"/>
+      <x:c r="AZ38" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ38" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA38" s="2"/>
+      <x:c r="BA38" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB38" s="2"/>
       <x:c r="BC38" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -10987,7 +11045,9 @@
       <x:c r="BL38" s="2"/>
       <x:c r="BM38" s="2"/>
       <x:c r="BN38" s="2"/>
-      <x:c r="BO38" s="2"/>
+      <x:c r="BO38" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP38" s="2"/>
       <x:c r="BQ38" s="2"/>
       <x:c r="BR38" s="2" t="n">
@@ -11043,7 +11103,7 @@
       <x:c r="CT38" s="2"/>
       <x:c r="CU38" s="2"/>
       <x:c r="CV38" s="2"/>
-      <x:c r="CW38" s="2" t="str"/>
+      <x:c r="CW38" s="2"/>
       <x:c r="CX38" s="2"/>
       <x:c r="CY38" s="2"/>
       <x:c r="CZ38" s="2"/>
@@ -11248,13 +11308,13 @@
       <x:c r="AV39" s="2"/>
       <x:c r="AW39" s="2"/>
       <x:c r="AX39" s="2"/>
-      <x:c r="AY39" s="2" t="str">
+      <x:c r="AY39" s="2" t="str"/>
+      <x:c r="AZ39" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ39" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA39" s="2"/>
+      <x:c r="BA39" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB39" s="2"/>
       <x:c r="BC39" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -11270,7 +11330,9 @@
       <x:c r="BL39" s="2"/>
       <x:c r="BM39" s="2"/>
       <x:c r="BN39" s="2"/>
-      <x:c r="BO39" s="2"/>
+      <x:c r="BO39" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP39" s="2"/>
       <x:c r="BQ39" s="2"/>
       <x:c r="BR39" s="2" t="n">
@@ -11324,7 +11386,7 @@
       <x:c r="CT39" s="2"/>
       <x:c r="CU39" s="2"/>
       <x:c r="CV39" s="2"/>
-      <x:c r="CW39" s="2" t="str"/>
+      <x:c r="CW39" s="2"/>
       <x:c r="CX39" s="2"/>
       <x:c r="CY39" s="2"/>
       <x:c r="CZ39" s="2"/>
@@ -11529,13 +11591,13 @@
       <x:c r="AV40" s="2"/>
       <x:c r="AW40" s="2"/>
       <x:c r="AX40" s="2"/>
-      <x:c r="AY40" s="2" t="str">
+      <x:c r="AY40" s="2" t="str"/>
+      <x:c r="AZ40" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ40" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA40" s="2"/>
+      <x:c r="BA40" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB40" s="2"/>
       <x:c r="BC40" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -11551,7 +11613,9 @@
       <x:c r="BL40" s="2"/>
       <x:c r="BM40" s="2"/>
       <x:c r="BN40" s="2"/>
-      <x:c r="BO40" s="2"/>
+      <x:c r="BO40" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP40" s="2"/>
       <x:c r="BQ40" s="2"/>
       <x:c r="BR40" s="2" t="n">
@@ -11607,7 +11671,7 @@
       <x:c r="CT40" s="2"/>
       <x:c r="CU40" s="2"/>
       <x:c r="CV40" s="2"/>
-      <x:c r="CW40" s="2" t="str"/>
+      <x:c r="CW40" s="2"/>
       <x:c r="CX40" s="2"/>
       <x:c r="CY40" s="2"/>
       <x:c r="CZ40" s="2"/>
@@ -11812,13 +11876,13 @@
       <x:c r="AV41" s="2"/>
       <x:c r="AW41" s="2"/>
       <x:c r="AX41" s="2"/>
-      <x:c r="AY41" s="2" t="str">
+      <x:c r="AY41" s="2" t="str"/>
+      <x:c r="AZ41" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ41" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA41" s="2"/>
+      <x:c r="BA41" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB41" s="2"/>
       <x:c r="BC41" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -11834,7 +11898,9 @@
       <x:c r="BL41" s="2"/>
       <x:c r="BM41" s="2"/>
       <x:c r="BN41" s="2"/>
-      <x:c r="BO41" s="2"/>
+      <x:c r="BO41" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP41" s="2"/>
       <x:c r="BQ41" s="2"/>
       <x:c r="BR41" s="2" t="n">
@@ -11888,7 +11954,7 @@
       <x:c r="CT41" s="2"/>
       <x:c r="CU41" s="2"/>
       <x:c r="CV41" s="2"/>
-      <x:c r="CW41" s="2" t="str"/>
+      <x:c r="CW41" s="2"/>
       <x:c r="CX41" s="2"/>
       <x:c r="CY41" s="2"/>
       <x:c r="CZ41" s="2"/>
@@ -12093,13 +12159,13 @@
       <x:c r="AV42" s="2"/>
       <x:c r="AW42" s="2"/>
       <x:c r="AX42" s="2"/>
-      <x:c r="AY42" s="2" t="str">
+      <x:c r="AY42" s="2" t="str"/>
+      <x:c r="AZ42" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ42" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA42" s="2"/>
+      <x:c r="BA42" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB42" s="2"/>
       <x:c r="BC42" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -12115,7 +12181,9 @@
       <x:c r="BL42" s="2"/>
       <x:c r="BM42" s="2"/>
       <x:c r="BN42" s="2"/>
-      <x:c r="BO42" s="2"/>
+      <x:c r="BO42" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP42" s="2"/>
       <x:c r="BQ42" s="2"/>
       <x:c r="BR42" s="2" t="n">
@@ -12170,7 +12238,7 @@
       <x:c r="CT42" s="2"/>
       <x:c r="CU42" s="2"/>
       <x:c r="CV42" s="2"/>
-      <x:c r="CW42" s="2" t="str"/>
+      <x:c r="CW42" s="2"/>
       <x:c r="CX42" s="2"/>
       <x:c r="CY42" s="2"/>
       <x:c r="CZ42" s="2"/>
@@ -12375,13 +12443,13 @@
       <x:c r="AV43" s="2"/>
       <x:c r="AW43" s="2"/>
       <x:c r="AX43" s="2"/>
-      <x:c r="AY43" s="2" t="str">
+      <x:c r="AY43" s="2" t="str"/>
+      <x:c r="AZ43" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ43" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA43" s="2"/>
+      <x:c r="BA43" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB43" s="2"/>
       <x:c r="BC43" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -12397,7 +12465,9 @@
       <x:c r="BL43" s="2"/>
       <x:c r="BM43" s="2"/>
       <x:c r="BN43" s="2"/>
-      <x:c r="BO43" s="2"/>
+      <x:c r="BO43" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP43" s="2"/>
       <x:c r="BQ43" s="2"/>
       <x:c r="BR43" s="2" t="n">
@@ -12453,7 +12523,7 @@
       <x:c r="CT43" s="2"/>
       <x:c r="CU43" s="2"/>
       <x:c r="CV43" s="2"/>
-      <x:c r="CW43" s="2" t="str"/>
+      <x:c r="CW43" s="2"/>
       <x:c r="CX43" s="2"/>
       <x:c r="CY43" s="2"/>
       <x:c r="CZ43" s="2"/>
@@ -12658,13 +12728,13 @@
       <x:c r="AV44" s="2"/>
       <x:c r="AW44" s="2"/>
       <x:c r="AX44" s="2"/>
-      <x:c r="AY44" s="2" t="str">
+      <x:c r="AY44" s="2" t="str"/>
+      <x:c r="AZ44" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ44" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA44" s="2"/>
+      <x:c r="BA44" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB44" s="2"/>
       <x:c r="BC44" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -12680,7 +12750,9 @@
       <x:c r="BL44" s="2"/>
       <x:c r="BM44" s="2"/>
       <x:c r="BN44" s="2"/>
-      <x:c r="BO44" s="2"/>
+      <x:c r="BO44" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP44" s="2"/>
       <x:c r="BQ44" s="2"/>
       <x:c r="BR44" s="2" t="n">
@@ -12736,7 +12808,7 @@
       <x:c r="CT44" s="2"/>
       <x:c r="CU44" s="2"/>
       <x:c r="CV44" s="2"/>
-      <x:c r="CW44" s="2" t="str"/>
+      <x:c r="CW44" s="2"/>
       <x:c r="CX44" s="2"/>
       <x:c r="CY44" s="2"/>
       <x:c r="CZ44" s="2"/>
@@ -12941,13 +13013,13 @@
       <x:c r="AV45" s="2"/>
       <x:c r="AW45" s="2"/>
       <x:c r="AX45" s="2"/>
-      <x:c r="AY45" s="2" t="str">
+      <x:c r="AY45" s="2" t="str"/>
+      <x:c r="AZ45" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ45" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA45" s="2"/>
+      <x:c r="BA45" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB45" s="2"/>
       <x:c r="BC45" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -12963,7 +13035,9 @@
       <x:c r="BL45" s="2"/>
       <x:c r="BM45" s="2"/>
       <x:c r="BN45" s="2"/>
-      <x:c r="BO45" s="2"/>
+      <x:c r="BO45" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP45" s="2"/>
       <x:c r="BQ45" s="2"/>
       <x:c r="BR45" s="2" t="n">
@@ -13019,7 +13093,7 @@
       <x:c r="CT45" s="2"/>
       <x:c r="CU45" s="2"/>
       <x:c r="CV45" s="2"/>
-      <x:c r="CW45" s="2" t="str"/>
+      <x:c r="CW45" s="2"/>
       <x:c r="CX45" s="2"/>
       <x:c r="CY45" s="2"/>
       <x:c r="CZ45" s="2"/>
@@ -13224,13 +13298,13 @@
       <x:c r="AV46" s="2"/>
       <x:c r="AW46" s="2"/>
       <x:c r="AX46" s="2"/>
-      <x:c r="AY46" s="2" t="str">
+      <x:c r="AY46" s="2" t="str"/>
+      <x:c r="AZ46" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ46" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA46" s="2"/>
+      <x:c r="BA46" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB46" s="2"/>
       <x:c r="BC46" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -13246,7 +13320,9 @@
       <x:c r="BL46" s="2"/>
       <x:c r="BM46" s="2"/>
       <x:c r="BN46" s="2"/>
-      <x:c r="BO46" s="2"/>
+      <x:c r="BO46" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP46" s="2"/>
       <x:c r="BQ46" s="2"/>
       <x:c r="BR46" s="2" t="n">
@@ -13300,7 +13376,7 @@
       <x:c r="CT46" s="2"/>
       <x:c r="CU46" s="2"/>
       <x:c r="CV46" s="2"/>
-      <x:c r="CW46" s="2" t="str"/>
+      <x:c r="CW46" s="2"/>
       <x:c r="CX46" s="2"/>
       <x:c r="CY46" s="2"/>
       <x:c r="CZ46" s="2"/>
@@ -13505,13 +13581,13 @@
       <x:c r="AV47" s="2"/>
       <x:c r="AW47" s="2"/>
       <x:c r="AX47" s="2"/>
-      <x:c r="AY47" s="2" t="str">
+      <x:c r="AY47" s="2" t="str"/>
+      <x:c r="AZ47" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ47" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA47" s="2"/>
+      <x:c r="BA47" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB47" s="2"/>
       <x:c r="BC47" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -13527,7 +13603,9 @@
       <x:c r="BL47" s="2"/>
       <x:c r="BM47" s="2"/>
       <x:c r="BN47" s="2"/>
-      <x:c r="BO47" s="2"/>
+      <x:c r="BO47" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP47" s="2"/>
       <x:c r="BQ47" s="2"/>
       <x:c r="BR47" s="2" t="n">
@@ -13584,7 +13662,7 @@
       <x:c r="CT47" s="2"/>
       <x:c r="CU47" s="2"/>
       <x:c r="CV47" s="2"/>
-      <x:c r="CW47" s="2" t="str"/>
+      <x:c r="CW47" s="2"/>
       <x:c r="CX47" s="2"/>
       <x:c r="CY47" s="2"/>
       <x:c r="CZ47" s="2"/>
@@ -13789,13 +13867,13 @@
       <x:c r="AV48" s="2"/>
       <x:c r="AW48" s="2"/>
       <x:c r="AX48" s="2"/>
-      <x:c r="AY48" s="2" t="str">
+      <x:c r="AY48" s="2" t="str"/>
+      <x:c r="AZ48" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ48" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA48" s="2"/>
+      <x:c r="BA48" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB48" s="2"/>
       <x:c r="BC48" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -13811,7 +13889,9 @@
       <x:c r="BL48" s="2"/>
       <x:c r="BM48" s="2"/>
       <x:c r="BN48" s="2"/>
-      <x:c r="BO48" s="2"/>
+      <x:c r="BO48" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP48" s="2"/>
       <x:c r="BQ48" s="2"/>
       <x:c r="BR48" s="2" t="n">
@@ -13868,7 +13948,7 @@
       <x:c r="CT48" s="2"/>
       <x:c r="CU48" s="2"/>
       <x:c r="CV48" s="2"/>
-      <x:c r="CW48" s="2" t="str"/>
+      <x:c r="CW48" s="2"/>
       <x:c r="CX48" s="2"/>
       <x:c r="CY48" s="2"/>
       <x:c r="CZ48" s="2"/>
@@ -14073,13 +14153,13 @@
       <x:c r="AV49" s="2"/>
       <x:c r="AW49" s="2"/>
       <x:c r="AX49" s="2"/>
-      <x:c r="AY49" s="2" t="str">
+      <x:c r="AY49" s="2" t="str"/>
+      <x:c r="AZ49" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ49" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA49" s="2"/>
+      <x:c r="BA49" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB49" s="2"/>
       <x:c r="BC49" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -14095,7 +14175,9 @@
       <x:c r="BL49" s="2"/>
       <x:c r="BM49" s="2"/>
       <x:c r="BN49" s="2"/>
-      <x:c r="BO49" s="2"/>
+      <x:c r="BO49" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP49" s="2"/>
       <x:c r="BQ49" s="2"/>
       <x:c r="BR49" s="2" t="n">
@@ -14152,7 +14234,7 @@
       <x:c r="CT49" s="2"/>
       <x:c r="CU49" s="2"/>
       <x:c r="CV49" s="2"/>
-      <x:c r="CW49" s="2" t="str"/>
+      <x:c r="CW49" s="2"/>
       <x:c r="CX49" s="2"/>
       <x:c r="CY49" s="2"/>
       <x:c r="CZ49" s="2"/>
@@ -14357,13 +14439,13 @@
       <x:c r="AV50" s="2"/>
       <x:c r="AW50" s="2"/>
       <x:c r="AX50" s="2"/>
-      <x:c r="AY50" s="2" t="str">
+      <x:c r="AY50" s="2" t="str"/>
+      <x:c r="AZ50" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ50" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA50" s="2"/>
+      <x:c r="BA50" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB50" s="2"/>
       <x:c r="BC50" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -14379,7 +14461,9 @@
       <x:c r="BL50" s="2"/>
       <x:c r="BM50" s="2"/>
       <x:c r="BN50" s="2"/>
-      <x:c r="BO50" s="2"/>
+      <x:c r="BO50" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP50" s="2"/>
       <x:c r="BQ50" s="2"/>
       <x:c r="BR50" s="2" t="n">
@@ -14437,7 +14521,7 @@
       <x:c r="CT50" s="2"/>
       <x:c r="CU50" s="2"/>
       <x:c r="CV50" s="2"/>
-      <x:c r="CW50" s="2" t="str"/>
+      <x:c r="CW50" s="2"/>
       <x:c r="CX50" s="2"/>
       <x:c r="CY50" s="2"/>
       <x:c r="CZ50" s="2"/>
@@ -14642,13 +14726,13 @@
       <x:c r="AV51" s="2"/>
       <x:c r="AW51" s="2"/>
       <x:c r="AX51" s="2"/>
-      <x:c r="AY51" s="2" t="str">
+      <x:c r="AY51" s="2" t="str"/>
+      <x:c r="AZ51" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ51" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA51" s="2"/>
+      <x:c r="BA51" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB51" s="2"/>
       <x:c r="BC51" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -14664,7 +14748,9 @@
       <x:c r="BL51" s="2"/>
       <x:c r="BM51" s="2"/>
       <x:c r="BN51" s="2"/>
-      <x:c r="BO51" s="2"/>
+      <x:c r="BO51" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP51" s="2"/>
       <x:c r="BQ51" s="2"/>
       <x:c r="BR51" s="2" t="n">
@@ -14720,7 +14806,7 @@
       <x:c r="CT51" s="2"/>
       <x:c r="CU51" s="2"/>
       <x:c r="CV51" s="2"/>
-      <x:c r="CW51" s="2" t="str"/>
+      <x:c r="CW51" s="2"/>
       <x:c r="CX51" s="2"/>
       <x:c r="CY51" s="2"/>
       <x:c r="CZ51" s="2"/>
@@ -14925,13 +15011,13 @@
       <x:c r="AV52" s="2"/>
       <x:c r="AW52" s="2"/>
       <x:c r="AX52" s="2"/>
-      <x:c r="AY52" s="2" t="str">
+      <x:c r="AY52" s="2" t="str"/>
+      <x:c r="AZ52" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ52" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA52" s="2"/>
+      <x:c r="BA52" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB52" s="2"/>
       <x:c r="BC52" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -14947,7 +15033,9 @@
       <x:c r="BL52" s="2"/>
       <x:c r="BM52" s="2"/>
       <x:c r="BN52" s="2"/>
-      <x:c r="BO52" s="2"/>
+      <x:c r="BO52" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP52" s="2"/>
       <x:c r="BQ52" s="2"/>
       <x:c r="BR52" s="2" t="n">
@@ -15002,7 +15090,7 @@
       <x:c r="CT52" s="2"/>
       <x:c r="CU52" s="2"/>
       <x:c r="CV52" s="2"/>
-      <x:c r="CW52" s="2" t="str"/>
+      <x:c r="CW52" s="2"/>
       <x:c r="CX52" s="2"/>
       <x:c r="CY52" s="2"/>
       <x:c r="CZ52" s="2"/>
@@ -15454,13 +15542,13 @@
       <x:c r="AV54" s="2"/>
       <x:c r="AW54" s="2"/>
       <x:c r="AX54" s="2"/>
-      <x:c r="AY54" s="2" t="str">
+      <x:c r="AY54" s="2" t="str"/>
+      <x:c r="AZ54" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ54" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA54" s="2"/>
+      <x:c r="BA54" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB54" s="2"/>
       <x:c r="BC54" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -15476,7 +15564,9 @@
       <x:c r="BL54" s="2"/>
       <x:c r="BM54" s="2"/>
       <x:c r="BN54" s="2"/>
-      <x:c r="BO54" s="2"/>
+      <x:c r="BO54" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP54" s="2"/>
       <x:c r="BQ54" s="2"/>
       <x:c r="BR54" s="2" t="n">
@@ -15535,7 +15625,7 @@
       <x:c r="CT54" s="2"/>
       <x:c r="CU54" s="2"/>
       <x:c r="CV54" s="2"/>
-      <x:c r="CW54" s="2" t="str"/>
+      <x:c r="CW54" s="2"/>
       <x:c r="CX54" s="2"/>
       <x:c r="CY54" s="2"/>
       <x:c r="CZ54" s="2"/>
@@ -15740,13 +15830,13 @@
       <x:c r="AV55" s="2"/>
       <x:c r="AW55" s="2"/>
       <x:c r="AX55" s="2"/>
-      <x:c r="AY55" s="2" t="str">
+      <x:c r="AY55" s="2" t="str"/>
+      <x:c r="AZ55" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ55" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA55" s="2"/>
+      <x:c r="BA55" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB55" s="2"/>
       <x:c r="BC55" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -15762,7 +15852,9 @@
       <x:c r="BL55" s="2"/>
       <x:c r="BM55" s="2"/>
       <x:c r="BN55" s="2"/>
-      <x:c r="BO55" s="2"/>
+      <x:c r="BO55" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP55" s="2"/>
       <x:c r="BQ55" s="2"/>
       <x:c r="BR55" s="2" t="n">
@@ -15817,7 +15909,7 @@
       <x:c r="CT55" s="2"/>
       <x:c r="CU55" s="2"/>
       <x:c r="CV55" s="2"/>
-      <x:c r="CW55" s="2" t="str"/>
+      <x:c r="CW55" s="2"/>
       <x:c r="CX55" s="2"/>
       <x:c r="CY55" s="2"/>
       <x:c r="CZ55" s="2"/>
@@ -16022,13 +16114,13 @@
       <x:c r="AV56" s="2"/>
       <x:c r="AW56" s="2"/>
       <x:c r="AX56" s="2"/>
-      <x:c r="AY56" s="2" t="str">
+      <x:c r="AY56" s="2" t="str"/>
+      <x:c r="AZ56" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ56" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA56" s="2"/>
+      <x:c r="BA56" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB56" s="2"/>
       <x:c r="BC56" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -16044,7 +16136,9 @@
       <x:c r="BL56" s="2"/>
       <x:c r="BM56" s="2"/>
       <x:c r="BN56" s="2"/>
-      <x:c r="BO56" s="2"/>
+      <x:c r="BO56" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP56" s="2"/>
       <x:c r="BQ56" s="2"/>
       <x:c r="BR56" s="2" t="n">
@@ -16098,7 +16192,7 @@
       <x:c r="CT56" s="2"/>
       <x:c r="CU56" s="2"/>
       <x:c r="CV56" s="2"/>
-      <x:c r="CW56" s="2" t="str"/>
+      <x:c r="CW56" s="2"/>
       <x:c r="CX56" s="2"/>
       <x:c r="CY56" s="2"/>
       <x:c r="CZ56" s="2"/>
@@ -16303,13 +16397,13 @@
       <x:c r="AV57" s="2"/>
       <x:c r="AW57" s="2"/>
       <x:c r="AX57" s="2"/>
-      <x:c r="AY57" s="2" t="str">
+      <x:c r="AY57" s="2" t="str"/>
+      <x:c r="AZ57" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ57" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA57" s="2"/>
+      <x:c r="BA57" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB57" s="2"/>
       <x:c r="BC57" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -16325,7 +16419,9 @@
       <x:c r="BL57" s="2"/>
       <x:c r="BM57" s="2"/>
       <x:c r="BN57" s="2"/>
-      <x:c r="BO57" s="2"/>
+      <x:c r="BO57" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP57" s="2"/>
       <x:c r="BQ57" s="2"/>
       <x:c r="BR57" s="2" t="n">
@@ -16382,7 +16478,7 @@
       <x:c r="CT57" s="2"/>
       <x:c r="CU57" s="2"/>
       <x:c r="CV57" s="2"/>
-      <x:c r="CW57" s="2" t="str"/>
+      <x:c r="CW57" s="2"/>
       <x:c r="CX57" s="2"/>
       <x:c r="CY57" s="2"/>
       <x:c r="CZ57" s="2"/>
@@ -16587,13 +16683,13 @@
       <x:c r="AV58" s="2"/>
       <x:c r="AW58" s="2"/>
       <x:c r="AX58" s="2"/>
-      <x:c r="AY58" s="2" t="str">
+      <x:c r="AY58" s="2" t="str"/>
+      <x:c r="AZ58" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ58" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA58" s="2"/>
+      <x:c r="BA58" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB58" s="2"/>
       <x:c r="BC58" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -16609,7 +16705,9 @@
       <x:c r="BL58" s="2"/>
       <x:c r="BM58" s="2"/>
       <x:c r="BN58" s="2"/>
-      <x:c r="BO58" s="2"/>
+      <x:c r="BO58" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP58" s="2"/>
       <x:c r="BQ58" s="2"/>
       <x:c r="BR58" s="2" t="n">
@@ -16665,7 +16763,7 @@
       <x:c r="CT58" s="2"/>
       <x:c r="CU58" s="2"/>
       <x:c r="CV58" s="2"/>
-      <x:c r="CW58" s="2" t="str"/>
+      <x:c r="CW58" s="2"/>
       <x:c r="CX58" s="2"/>
       <x:c r="CY58" s="2"/>
       <x:c r="CZ58" s="2"/>
@@ -16870,13 +16968,13 @@
       <x:c r="AV59" s="2"/>
       <x:c r="AW59" s="2"/>
       <x:c r="AX59" s="2"/>
-      <x:c r="AY59" s="2" t="str">
+      <x:c r="AY59" s="2" t="str"/>
+      <x:c r="AZ59" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ59" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA59" s="2"/>
+      <x:c r="BA59" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB59" s="2"/>
       <x:c r="BC59" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -16892,7 +16990,9 @@
       <x:c r="BL59" s="2"/>
       <x:c r="BM59" s="2"/>
       <x:c r="BN59" s="2"/>
-      <x:c r="BO59" s="2"/>
+      <x:c r="BO59" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP59" s="2"/>
       <x:c r="BQ59" s="2"/>
       <x:c r="BR59" s="2" t="n">
@@ -16946,7 +17046,7 @@
       <x:c r="CT59" s="2"/>
       <x:c r="CU59" s="2"/>
       <x:c r="CV59" s="2"/>
-      <x:c r="CW59" s="2" t="str"/>
+      <x:c r="CW59" s="2"/>
       <x:c r="CX59" s="2"/>
       <x:c r="CY59" s="2"/>
       <x:c r="CZ59" s="2"/>
@@ -17151,13 +17251,13 @@
       <x:c r="AV60" s="2"/>
       <x:c r="AW60" s="2"/>
       <x:c r="AX60" s="2"/>
-      <x:c r="AY60" s="2" t="str">
+      <x:c r="AY60" s="2" t="str"/>
+      <x:c r="AZ60" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ60" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA60" s="2"/>
+      <x:c r="BA60" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB60" s="2"/>
       <x:c r="BC60" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -17173,7 +17273,9 @@
       <x:c r="BL60" s="2"/>
       <x:c r="BM60" s="2"/>
       <x:c r="BN60" s="2"/>
-      <x:c r="BO60" s="2"/>
+      <x:c r="BO60" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP60" s="2"/>
       <x:c r="BQ60" s="2"/>
       <x:c r="BR60" s="2" t="n">
@@ -17229,7 +17331,7 @@
       <x:c r="CT60" s="2"/>
       <x:c r="CU60" s="2"/>
       <x:c r="CV60" s="2"/>
-      <x:c r="CW60" s="2" t="str"/>
+      <x:c r="CW60" s="2"/>
       <x:c r="CX60" s="2"/>
       <x:c r="CY60" s="2"/>
       <x:c r="CZ60" s="2"/>
@@ -17434,13 +17536,13 @@
       <x:c r="AV61" s="2"/>
       <x:c r="AW61" s="2"/>
       <x:c r="AX61" s="2"/>
-      <x:c r="AY61" s="2" t="str">
+      <x:c r="AY61" s="2" t="str"/>
+      <x:c r="AZ61" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ61" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA61" s="2"/>
+      <x:c r="BA61" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB61" s="2"/>
       <x:c r="BC61" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -17456,7 +17558,9 @@
       <x:c r="BL61" s="2"/>
       <x:c r="BM61" s="2"/>
       <x:c r="BN61" s="2"/>
-      <x:c r="BO61" s="2"/>
+      <x:c r="BO61" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP61" s="2"/>
       <x:c r="BQ61" s="2"/>
       <x:c r="BR61" s="2" t="n">
@@ -17511,7 +17615,7 @@
       <x:c r="CT61" s="2"/>
       <x:c r="CU61" s="2"/>
       <x:c r="CV61" s="2"/>
-      <x:c r="CW61" s="2" t="str"/>
+      <x:c r="CW61" s="2"/>
       <x:c r="CX61" s="2"/>
       <x:c r="CY61" s="2"/>
       <x:c r="CZ61" s="2"/>
@@ -17716,13 +17820,13 @@
       <x:c r="AV62" s="2"/>
       <x:c r="AW62" s="2"/>
       <x:c r="AX62" s="2"/>
-      <x:c r="AY62" s="2" t="str">
+      <x:c r="AY62" s="2" t="str"/>
+      <x:c r="AZ62" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ62" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA62" s="2"/>
+      <x:c r="BA62" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB62" s="2"/>
       <x:c r="BC62" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -17738,7 +17842,9 @@
       <x:c r="BL62" s="2"/>
       <x:c r="BM62" s="2"/>
       <x:c r="BN62" s="2"/>
-      <x:c r="BO62" s="2"/>
+      <x:c r="BO62" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP62" s="2"/>
       <x:c r="BQ62" s="2"/>
       <x:c r="BR62" s="2" t="n">
@@ -17792,7 +17898,7 @@
       <x:c r="CT62" s="2"/>
       <x:c r="CU62" s="2"/>
       <x:c r="CV62" s="2"/>
-      <x:c r="CW62" s="2" t="str"/>
+      <x:c r="CW62" s="2"/>
       <x:c r="CX62" s="2"/>
       <x:c r="CY62" s="2"/>
       <x:c r="CZ62" s="2"/>
@@ -18244,13 +18350,13 @@
       <x:c r="AV64" s="2"/>
       <x:c r="AW64" s="2"/>
       <x:c r="AX64" s="2"/>
-      <x:c r="AY64" s="2" t="str">
+      <x:c r="AY64" s="2" t="str"/>
+      <x:c r="AZ64" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ64" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA64" s="2"/>
+      <x:c r="BA64" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB64" s="2"/>
       <x:c r="BC64" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -18266,7 +18372,9 @@
       <x:c r="BL64" s="2"/>
       <x:c r="BM64" s="2"/>
       <x:c r="BN64" s="2"/>
-      <x:c r="BO64" s="2"/>
+      <x:c r="BO64" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP64" s="2"/>
       <x:c r="BQ64" s="2"/>
       <x:c r="BR64" s="2" t="n">
@@ -18322,7 +18430,7 @@
       <x:c r="CT64" s="2"/>
       <x:c r="CU64" s="2"/>
       <x:c r="CV64" s="2"/>
-      <x:c r="CW64" s="2" t="str"/>
+      <x:c r="CW64" s="2"/>
       <x:c r="CX64" s="2"/>
       <x:c r="CY64" s="2"/>
       <x:c r="CZ64" s="2"/>
@@ -18527,13 +18635,13 @@
       <x:c r="AV65" s="2"/>
       <x:c r="AW65" s="2"/>
       <x:c r="AX65" s="2"/>
-      <x:c r="AY65" s="2" t="str">
+      <x:c r="AY65" s="2" t="str"/>
+      <x:c r="AZ65" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ65" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA65" s="2"/>
+      <x:c r="BA65" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB65" s="2"/>
       <x:c r="BC65" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -18549,7 +18657,9 @@
       <x:c r="BL65" s="2"/>
       <x:c r="BM65" s="2"/>
       <x:c r="BN65" s="2"/>
-      <x:c r="BO65" s="2"/>
+      <x:c r="BO65" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP65" s="2"/>
       <x:c r="BQ65" s="2"/>
       <x:c r="BR65" s="2" t="n">
@@ -18605,7 +18715,7 @@
       <x:c r="CT65" s="2"/>
       <x:c r="CU65" s="2"/>
       <x:c r="CV65" s="2"/>
-      <x:c r="CW65" s="2" t="str"/>
+      <x:c r="CW65" s="2"/>
       <x:c r="CX65" s="2"/>
       <x:c r="CY65" s="2"/>
       <x:c r="CZ65" s="2"/>
@@ -18810,13 +18920,13 @@
       <x:c r="AV66" s="2"/>
       <x:c r="AW66" s="2"/>
       <x:c r="AX66" s="2"/>
-      <x:c r="AY66" s="2" t="str">
+      <x:c r="AY66" s="2" t="str"/>
+      <x:c r="AZ66" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ66" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA66" s="2"/>
+      <x:c r="BA66" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB66" s="2"/>
       <x:c r="BC66" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -18832,7 +18942,9 @@
       <x:c r="BL66" s="2"/>
       <x:c r="BM66" s="2"/>
       <x:c r="BN66" s="2"/>
-      <x:c r="BO66" s="2"/>
+      <x:c r="BO66" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP66" s="2"/>
       <x:c r="BQ66" s="2"/>
       <x:c r="BR66" s="2" t="n">
@@ -18888,7 +19000,7 @@
       <x:c r="CT66" s="2"/>
       <x:c r="CU66" s="2"/>
       <x:c r="CV66" s="2"/>
-      <x:c r="CW66" s="2" t="str"/>
+      <x:c r="CW66" s="2"/>
       <x:c r="CX66" s="2"/>
       <x:c r="CY66" s="2"/>
       <x:c r="CZ66" s="2"/>
@@ -19093,13 +19205,13 @@
       <x:c r="AV67" s="2"/>
       <x:c r="AW67" s="2"/>
       <x:c r="AX67" s="2"/>
-      <x:c r="AY67" s="2" t="str">
+      <x:c r="AY67" s="2" t="str"/>
+      <x:c r="AZ67" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ67" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA67" s="2"/>
+      <x:c r="BA67" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB67" s="2"/>
       <x:c r="BC67" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -19115,7 +19227,9 @@
       <x:c r="BL67" s="2"/>
       <x:c r="BM67" s="2"/>
       <x:c r="BN67" s="2"/>
-      <x:c r="BO67" s="2"/>
+      <x:c r="BO67" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP67" s="2"/>
       <x:c r="BQ67" s="2"/>
       <x:c r="BR67" s="2" t="n">
@@ -19172,7 +19286,7 @@
       <x:c r="CT67" s="2"/>
       <x:c r="CU67" s="2"/>
       <x:c r="CV67" s="2"/>
-      <x:c r="CW67" s="2" t="str"/>
+      <x:c r="CW67" s="2"/>
       <x:c r="CX67" s="2"/>
       <x:c r="CY67" s="2"/>
       <x:c r="CZ67" s="2"/>
@@ -19377,13 +19491,13 @@
       <x:c r="AV68" s="2"/>
       <x:c r="AW68" s="2"/>
       <x:c r="AX68" s="2"/>
-      <x:c r="AY68" s="2" t="str">
+      <x:c r="AY68" s="2" t="str"/>
+      <x:c r="AZ68" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ68" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA68" s="2"/>
+      <x:c r="BA68" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB68" s="2"/>
       <x:c r="BC68" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -19399,7 +19513,9 @@
       <x:c r="BL68" s="2"/>
       <x:c r="BM68" s="2"/>
       <x:c r="BN68" s="2"/>
-      <x:c r="BO68" s="2"/>
+      <x:c r="BO68" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP68" s="2"/>
       <x:c r="BQ68" s="2"/>
       <x:c r="BR68" s="2" t="n">
@@ -19456,7 +19572,7 @@
       <x:c r="CT68" s="2"/>
       <x:c r="CU68" s="2"/>
       <x:c r="CV68" s="2"/>
-      <x:c r="CW68" s="2" t="str"/>
+      <x:c r="CW68" s="2"/>
       <x:c r="CX68" s="2"/>
       <x:c r="CY68" s="2"/>
       <x:c r="CZ68" s="2"/>
@@ -19661,13 +19777,13 @@
       <x:c r="AV69" s="2"/>
       <x:c r="AW69" s="2"/>
       <x:c r="AX69" s="2"/>
-      <x:c r="AY69" s="2" t="str">
+      <x:c r="AY69" s="2" t="str"/>
+      <x:c r="AZ69" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ69" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA69" s="2"/>
+      <x:c r="BA69" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB69" s="2"/>
       <x:c r="BC69" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -19683,7 +19799,9 @@
       <x:c r="BL69" s="2"/>
       <x:c r="BM69" s="2"/>
       <x:c r="BN69" s="2"/>
-      <x:c r="BO69" s="2"/>
+      <x:c r="BO69" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP69" s="2"/>
       <x:c r="BQ69" s="2"/>
       <x:c r="BR69" s="2" t="n">
@@ -19739,7 +19857,7 @@
       <x:c r="CT69" s="2"/>
       <x:c r="CU69" s="2"/>
       <x:c r="CV69" s="2"/>
-      <x:c r="CW69" s="2" t="str"/>
+      <x:c r="CW69" s="2"/>
       <x:c r="CX69" s="2"/>
       <x:c r="CY69" s="2"/>
       <x:c r="CZ69" s="2"/>
@@ -19944,13 +20062,13 @@
       <x:c r="AV70" s="2"/>
       <x:c r="AW70" s="2"/>
       <x:c r="AX70" s="2"/>
-      <x:c r="AY70" s="2" t="str">
+      <x:c r="AY70" s="2" t="str"/>
+      <x:c r="AZ70" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ70" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA70" s="2"/>
+      <x:c r="BA70" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB70" s="2"/>
       <x:c r="BC70" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -19966,7 +20084,9 @@
       <x:c r="BL70" s="2"/>
       <x:c r="BM70" s="2"/>
       <x:c r="BN70" s="2"/>
-      <x:c r="BO70" s="2"/>
+      <x:c r="BO70" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP70" s="2"/>
       <x:c r="BQ70" s="2"/>
       <x:c r="BR70" s="2" t="n">
@@ -20021,7 +20141,7 @@
       <x:c r="CT70" s="2"/>
       <x:c r="CU70" s="2"/>
       <x:c r="CV70" s="2"/>
-      <x:c r="CW70" s="2" t="str"/>
+      <x:c r="CW70" s="2"/>
       <x:c r="CX70" s="2"/>
       <x:c r="CY70" s="2"/>
       <x:c r="CZ70" s="2"/>
@@ -20226,13 +20346,13 @@
       <x:c r="AV71" s="2"/>
       <x:c r="AW71" s="2"/>
       <x:c r="AX71" s="2"/>
-      <x:c r="AY71" s="2" t="str">
+      <x:c r="AY71" s="2" t="str"/>
+      <x:c r="AZ71" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ71" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA71" s="2"/>
+      <x:c r="BA71" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB71" s="2"/>
       <x:c r="BC71" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -20248,7 +20368,9 @@
       <x:c r="BL71" s="2"/>
       <x:c r="BM71" s="2"/>
       <x:c r="BN71" s="2"/>
-      <x:c r="BO71" s="2"/>
+      <x:c r="BO71" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP71" s="2"/>
       <x:c r="BQ71" s="2"/>
       <x:c r="BR71" s="2" t="n">
@@ -20302,7 +20424,7 @@
       <x:c r="CT71" s="2"/>
       <x:c r="CU71" s="2"/>
       <x:c r="CV71" s="2"/>
-      <x:c r="CW71" s="2" t="str"/>
+      <x:c r="CW71" s="2"/>
       <x:c r="CX71" s="2"/>
       <x:c r="CY71" s="2"/>
       <x:c r="CZ71" s="2"/>
@@ -20507,13 +20629,13 @@
       <x:c r="AV72" s="2"/>
       <x:c r="AW72" s="2"/>
       <x:c r="AX72" s="2"/>
-      <x:c r="AY72" s="2" t="str">
+      <x:c r="AY72" s="2" t="str"/>
+      <x:c r="AZ72" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ72" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA72" s="2"/>
+      <x:c r="BA72" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB72" s="2"/>
       <x:c r="BC72" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -20529,7 +20651,9 @@
       <x:c r="BL72" s="2"/>
       <x:c r="BM72" s="2"/>
       <x:c r="BN72" s="2"/>
-      <x:c r="BO72" s="2"/>
+      <x:c r="BO72" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP72" s="2"/>
       <x:c r="BQ72" s="2"/>
       <x:c r="BR72" s="2" t="n">
@@ -20583,7 +20707,7 @@
       <x:c r="CT72" s="2"/>
       <x:c r="CU72" s="2"/>
       <x:c r="CV72" s="2"/>
-      <x:c r="CW72" s="2" t="str"/>
+      <x:c r="CW72" s="2"/>
       <x:c r="CX72" s="2"/>
       <x:c r="CY72" s="2"/>
       <x:c r="CZ72" s="2"/>
@@ -20788,13 +20912,13 @@
       <x:c r="AV73" s="2"/>
       <x:c r="AW73" s="2"/>
       <x:c r="AX73" s="2"/>
-      <x:c r="AY73" s="2" t="str">
+      <x:c r="AY73" s="2" t="str"/>
+      <x:c r="AZ73" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ73" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA73" s="2"/>
+      <x:c r="BA73" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB73" s="2"/>
       <x:c r="BC73" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -20810,7 +20934,9 @@
       <x:c r="BL73" s="2"/>
       <x:c r="BM73" s="2"/>
       <x:c r="BN73" s="2"/>
-      <x:c r="BO73" s="2"/>
+      <x:c r="BO73" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP73" s="2"/>
       <x:c r="BQ73" s="2"/>
       <x:c r="BR73" s="2" t="n">
@@ -20863,7 +20989,7 @@
       <x:c r="CT73" s="2"/>
       <x:c r="CU73" s="2"/>
       <x:c r="CV73" s="2"/>
-      <x:c r="CW73" s="2" t="str"/>
+      <x:c r="CW73" s="2"/>
       <x:c r="CX73" s="2"/>
       <x:c r="CY73" s="2"/>
       <x:c r="CZ73" s="2"/>
@@ -21068,13 +21194,13 @@
       <x:c r="AV74" s="2"/>
       <x:c r="AW74" s="2"/>
       <x:c r="AX74" s="2"/>
-      <x:c r="AY74" s="2" t="str">
+      <x:c r="AY74" s="2" t="str"/>
+      <x:c r="AZ74" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ74" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA74" s="2"/>
+      <x:c r="BA74" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB74" s="2"/>
       <x:c r="BC74" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -21090,7 +21216,9 @@
       <x:c r="BL74" s="2"/>
       <x:c r="BM74" s="2"/>
       <x:c r="BN74" s="2"/>
-      <x:c r="BO74" s="2"/>
+      <x:c r="BO74" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP74" s="2"/>
       <x:c r="BQ74" s="2"/>
       <x:c r="BR74" s="2" t="n">
@@ -21145,7 +21273,7 @@
       <x:c r="CT74" s="2"/>
       <x:c r="CU74" s="2"/>
       <x:c r="CV74" s="2"/>
-      <x:c r="CW74" s="2" t="str"/>
+      <x:c r="CW74" s="2"/>
       <x:c r="CX74" s="2"/>
       <x:c r="CY74" s="2"/>
       <x:c r="CZ74" s="2"/>
@@ -21350,13 +21478,13 @@
       <x:c r="AV75" s="2"/>
       <x:c r="AW75" s="2"/>
       <x:c r="AX75" s="2"/>
-      <x:c r="AY75" s="2" t="str">
+      <x:c r="AY75" s="2" t="str"/>
+      <x:c r="AZ75" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ75" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA75" s="2"/>
+      <x:c r="BA75" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB75" s="2"/>
       <x:c r="BC75" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -21372,7 +21500,9 @@
       <x:c r="BL75" s="2"/>
       <x:c r="BM75" s="2"/>
       <x:c r="BN75" s="2"/>
-      <x:c r="BO75" s="2"/>
+      <x:c r="BO75" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP75" s="2"/>
       <x:c r="BQ75" s="2"/>
       <x:c r="BR75" s="2" t="n">
@@ -21426,7 +21556,7 @@
       <x:c r="CT75" s="2"/>
       <x:c r="CU75" s="2"/>
       <x:c r="CV75" s="2"/>
-      <x:c r="CW75" s="2" t="str"/>
+      <x:c r="CW75" s="2"/>
       <x:c r="CX75" s="2"/>
       <x:c r="CY75" s="2"/>
       <x:c r="CZ75" s="2"/>
@@ -21631,13 +21761,13 @@
       <x:c r="AV76" s="2"/>
       <x:c r="AW76" s="2"/>
       <x:c r="AX76" s="2"/>
-      <x:c r="AY76" s="2" t="str">
+      <x:c r="AY76" s="2" t="str"/>
+      <x:c r="AZ76" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ76" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA76" s="2"/>
+      <x:c r="BA76" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB76" s="2"/>
       <x:c r="BC76" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -21653,7 +21783,9 @@
       <x:c r="BL76" s="2"/>
       <x:c r="BM76" s="2"/>
       <x:c r="BN76" s="2"/>
-      <x:c r="BO76" s="2"/>
+      <x:c r="BO76" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP76" s="2"/>
       <x:c r="BQ76" s="2"/>
       <x:c r="BR76" s="2" t="n">
@@ -21707,7 +21839,7 @@
       <x:c r="CT76" s="2"/>
       <x:c r="CU76" s="2"/>
       <x:c r="CV76" s="2"/>
-      <x:c r="CW76" s="2" t="str"/>
+      <x:c r="CW76" s="2"/>
       <x:c r="CX76" s="2"/>
       <x:c r="CY76" s="2"/>
       <x:c r="CZ76" s="2"/>
@@ -21912,13 +22044,13 @@
       <x:c r="AV77" s="2"/>
       <x:c r="AW77" s="2"/>
       <x:c r="AX77" s="2"/>
-      <x:c r="AY77" s="2" t="str">
+      <x:c r="AY77" s="2" t="str"/>
+      <x:c r="AZ77" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ77" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA77" s="2"/>
+      <x:c r="BA77" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB77" s="2"/>
       <x:c r="BC77" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -21934,7 +22066,9 @@
       <x:c r="BL77" s="2"/>
       <x:c r="BM77" s="2"/>
       <x:c r="BN77" s="2"/>
-      <x:c r="BO77" s="2"/>
+      <x:c r="BO77" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP77" s="2"/>
       <x:c r="BQ77" s="2"/>
       <x:c r="BR77" s="2" t="n">
@@ -21989,7 +22123,7 @@
       <x:c r="CT77" s="2"/>
       <x:c r="CU77" s="2"/>
       <x:c r="CV77" s="2"/>
-      <x:c r="CW77" s="2" t="str"/>
+      <x:c r="CW77" s="2"/>
       <x:c r="CX77" s="2"/>
       <x:c r="CY77" s="2"/>
       <x:c r="CZ77" s="2"/>
@@ -22194,13 +22328,13 @@
       <x:c r="AV78" s="2"/>
       <x:c r="AW78" s="2"/>
       <x:c r="AX78" s="2"/>
-      <x:c r="AY78" s="2" t="str">
+      <x:c r="AY78" s="2" t="str"/>
+      <x:c r="AZ78" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ78" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA78" s="2"/>
+      <x:c r="BA78" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB78" s="2"/>
       <x:c r="BC78" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -22216,7 +22350,9 @@
       <x:c r="BL78" s="2"/>
       <x:c r="BM78" s="2"/>
       <x:c r="BN78" s="2"/>
-      <x:c r="BO78" s="2"/>
+      <x:c r="BO78" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP78" s="2"/>
       <x:c r="BQ78" s="2"/>
       <x:c r="BR78" s="2" t="n">
@@ -22270,7 +22406,7 @@
       <x:c r="CT78" s="2"/>
       <x:c r="CU78" s="2"/>
       <x:c r="CV78" s="2"/>
-      <x:c r="CW78" s="2" t="str"/>
+      <x:c r="CW78" s="2"/>
       <x:c r="CX78" s="2"/>
       <x:c r="CY78" s="2"/>
       <x:c r="CZ78" s="2"/>
@@ -22475,13 +22611,13 @@
       <x:c r="AV79" s="2"/>
       <x:c r="AW79" s="2"/>
       <x:c r="AX79" s="2"/>
-      <x:c r="AY79" s="2" t="str">
+      <x:c r="AY79" s="2" t="str"/>
+      <x:c r="AZ79" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ79" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA79" s="2"/>
+      <x:c r="BA79" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB79" s="2"/>
       <x:c r="BC79" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -22497,7 +22633,9 @@
       <x:c r="BL79" s="2"/>
       <x:c r="BM79" s="2"/>
       <x:c r="BN79" s="2"/>
-      <x:c r="BO79" s="2"/>
+      <x:c r="BO79" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP79" s="2"/>
       <x:c r="BQ79" s="2"/>
       <x:c r="BR79" s="2" t="n">
@@ -22552,7 +22690,7 @@
       <x:c r="CT79" s="2"/>
       <x:c r="CU79" s="2"/>
       <x:c r="CV79" s="2"/>
-      <x:c r="CW79" s="2" t="str"/>
+      <x:c r="CW79" s="2"/>
       <x:c r="CX79" s="2"/>
       <x:c r="CY79" s="2"/>
       <x:c r="CZ79" s="2"/>
@@ -22757,13 +22895,13 @@
       <x:c r="AV80" s="2"/>
       <x:c r="AW80" s="2"/>
       <x:c r="AX80" s="2"/>
-      <x:c r="AY80" s="2" t="str">
+      <x:c r="AY80" s="2" t="str"/>
+      <x:c r="AZ80" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ80" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA80" s="2"/>
+      <x:c r="BA80" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB80" s="2"/>
       <x:c r="BC80" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -22779,7 +22917,9 @@
       <x:c r="BL80" s="2"/>
       <x:c r="BM80" s="2"/>
       <x:c r="BN80" s="2"/>
-      <x:c r="BO80" s="2"/>
+      <x:c r="BO80" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP80" s="2"/>
       <x:c r="BQ80" s="2"/>
       <x:c r="BR80" s="2" t="n">
@@ -22835,7 +22975,7 @@
       <x:c r="CT80" s="2"/>
       <x:c r="CU80" s="2"/>
       <x:c r="CV80" s="2"/>
-      <x:c r="CW80" s="2" t="str"/>
+      <x:c r="CW80" s="2"/>
       <x:c r="CX80" s="2"/>
       <x:c r="CY80" s="2"/>
       <x:c r="CZ80" s="2"/>
@@ -23040,13 +23180,13 @@
       <x:c r="AV81" s="2"/>
       <x:c r="AW81" s="2"/>
       <x:c r="AX81" s="2"/>
-      <x:c r="AY81" s="2" t="str">
+      <x:c r="AY81" s="2" t="str"/>
+      <x:c r="AZ81" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ81" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA81" s="2"/>
+      <x:c r="BA81" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB81" s="2"/>
       <x:c r="BC81" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -23062,7 +23202,9 @@
       <x:c r="BL81" s="2"/>
       <x:c r="BM81" s="2"/>
       <x:c r="BN81" s="2"/>
-      <x:c r="BO81" s="2"/>
+      <x:c r="BO81" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP81" s="2"/>
       <x:c r="BQ81" s="2"/>
       <x:c r="BR81" s="2" t="n">
@@ -23114,7 +23256,7 @@
       <x:c r="CT81" s="2"/>
       <x:c r="CU81" s="2"/>
       <x:c r="CV81" s="2"/>
-      <x:c r="CW81" s="2" t="str"/>
+      <x:c r="CW81" s="2"/>
       <x:c r="CX81" s="2"/>
       <x:c r="CY81" s="2"/>
       <x:c r="CZ81" s="2"/>
@@ -23319,13 +23461,13 @@
       <x:c r="AV82" s="2"/>
       <x:c r="AW82" s="2"/>
       <x:c r="AX82" s="2"/>
-      <x:c r="AY82" s="2" t="str">
+      <x:c r="AY82" s="2" t="str"/>
+      <x:c r="AZ82" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ82" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA82" s="2"/>
+      <x:c r="BA82" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB82" s="2"/>
       <x:c r="BC82" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -23341,7 +23483,9 @@
       <x:c r="BL82" s="2"/>
       <x:c r="BM82" s="2"/>
       <x:c r="BN82" s="2"/>
-      <x:c r="BO82" s="2"/>
+      <x:c r="BO82" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP82" s="2"/>
       <x:c r="BQ82" s="2"/>
       <x:c r="BR82" s="2" t="n">
@@ -23397,7 +23541,7 @@
       <x:c r="CT82" s="2"/>
       <x:c r="CU82" s="2"/>
       <x:c r="CV82" s="2"/>
-      <x:c r="CW82" s="2" t="str"/>
+      <x:c r="CW82" s="2"/>
       <x:c r="CX82" s="2"/>
       <x:c r="CY82" s="2"/>
       <x:c r="CZ82" s="2"/>
@@ -23602,13 +23746,13 @@
       <x:c r="AV83" s="2"/>
       <x:c r="AW83" s="2"/>
       <x:c r="AX83" s="2"/>
-      <x:c r="AY83" s="2" t="str">
+      <x:c r="AY83" s="2" t="str"/>
+      <x:c r="AZ83" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ83" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA83" s="2"/>
+      <x:c r="BA83" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB83" s="2"/>
       <x:c r="BC83" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -23624,7 +23768,9 @@
       <x:c r="BL83" s="2"/>
       <x:c r="BM83" s="2"/>
       <x:c r="BN83" s="2"/>
-      <x:c r="BO83" s="2"/>
+      <x:c r="BO83" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP83" s="2"/>
       <x:c r="BQ83" s="2"/>
       <x:c r="BR83" s="2" t="n">
@@ -23678,7 +23824,7 @@
       <x:c r="CT83" s="2"/>
       <x:c r="CU83" s="2"/>
       <x:c r="CV83" s="2"/>
-      <x:c r="CW83" s="2" t="str"/>
+      <x:c r="CW83" s="2"/>
       <x:c r="CX83" s="2"/>
       <x:c r="CY83" s="2"/>
       <x:c r="CZ83" s="2"/>
@@ -23883,13 +24029,13 @@
       <x:c r="AV84" s="2"/>
       <x:c r="AW84" s="2"/>
       <x:c r="AX84" s="2"/>
-      <x:c r="AY84" s="2" t="str">
+      <x:c r="AY84" s="2" t="str"/>
+      <x:c r="AZ84" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ84" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA84" s="2"/>
+      <x:c r="BA84" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB84" s="2"/>
       <x:c r="BC84" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -23905,7 +24051,9 @@
       <x:c r="BL84" s="2"/>
       <x:c r="BM84" s="2"/>
       <x:c r="BN84" s="2"/>
-      <x:c r="BO84" s="2"/>
+      <x:c r="BO84" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP84" s="2"/>
       <x:c r="BQ84" s="2"/>
       <x:c r="BR84" s="2" t="n">
@@ -23962,7 +24110,7 @@
       <x:c r="CT84" s="2"/>
       <x:c r="CU84" s="2"/>
       <x:c r="CV84" s="2"/>
-      <x:c r="CW84" s="2" t="str"/>
+      <x:c r="CW84" s="2"/>
       <x:c r="CX84" s="2"/>
       <x:c r="CY84" s="2"/>
       <x:c r="CZ84" s="2"/>
@@ -24167,13 +24315,13 @@
       <x:c r="AV85" s="2"/>
       <x:c r="AW85" s="2"/>
       <x:c r="AX85" s="2"/>
-      <x:c r="AY85" s="2" t="str">
+      <x:c r="AY85" s="2" t="str"/>
+      <x:c r="AZ85" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ85" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA85" s="2"/>
+      <x:c r="BA85" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB85" s="2"/>
       <x:c r="BC85" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -24189,7 +24337,9 @@
       <x:c r="BL85" s="2"/>
       <x:c r="BM85" s="2"/>
       <x:c r="BN85" s="2"/>
-      <x:c r="BO85" s="2"/>
+      <x:c r="BO85" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP85" s="2"/>
       <x:c r="BQ85" s="2"/>
       <x:c r="BR85" s="2" t="n">
@@ -24245,7 +24395,7 @@
       <x:c r="CT85" s="2"/>
       <x:c r="CU85" s="2"/>
       <x:c r="CV85" s="2"/>
-      <x:c r="CW85" s="2" t="str"/>
+      <x:c r="CW85" s="2"/>
       <x:c r="CX85" s="2"/>
       <x:c r="CY85" s="2"/>
       <x:c r="CZ85" s="2"/>
@@ -24450,13 +24600,13 @@
       <x:c r="AV86" s="2"/>
       <x:c r="AW86" s="2"/>
       <x:c r="AX86" s="2"/>
-      <x:c r="AY86" s="2" t="str">
+      <x:c r="AY86" s="2" t="str"/>
+      <x:c r="AZ86" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ86" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA86" s="2"/>
+      <x:c r="BA86" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB86" s="2"/>
       <x:c r="BC86" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -24472,7 +24622,9 @@
       <x:c r="BL86" s="2"/>
       <x:c r="BM86" s="2"/>
       <x:c r="BN86" s="2"/>
-      <x:c r="BO86" s="2"/>
+      <x:c r="BO86" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP86" s="2"/>
       <x:c r="BQ86" s="2"/>
       <x:c r="BR86" s="2" t="n">
@@ -24528,7 +24680,7 @@
       <x:c r="CT86" s="2"/>
       <x:c r="CU86" s="2"/>
       <x:c r="CV86" s="2"/>
-      <x:c r="CW86" s="2" t="str"/>
+      <x:c r="CW86" s="2"/>
       <x:c r="CX86" s="2"/>
       <x:c r="CY86" s="2"/>
       <x:c r="CZ86" s="2"/>
@@ -24733,13 +24885,13 @@
       <x:c r="AV87" s="2"/>
       <x:c r="AW87" s="2"/>
       <x:c r="AX87" s="2"/>
-      <x:c r="AY87" s="2" t="str">
+      <x:c r="AY87" s="2" t="str"/>
+      <x:c r="AZ87" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ87" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA87" s="2"/>
+      <x:c r="BA87" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB87" s="2"/>
       <x:c r="BC87" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -24755,7 +24907,9 @@
       <x:c r="BL87" s="2"/>
       <x:c r="BM87" s="2"/>
       <x:c r="BN87" s="2"/>
-      <x:c r="BO87" s="2"/>
+      <x:c r="BO87" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP87" s="2"/>
       <x:c r="BQ87" s="2"/>
       <x:c r="BR87" s="2" t="n">
@@ -24810,7 +24964,7 @@
       <x:c r="CT87" s="2"/>
       <x:c r="CU87" s="2"/>
       <x:c r="CV87" s="2"/>
-      <x:c r="CW87" s="2" t="str"/>
+      <x:c r="CW87" s="2"/>
       <x:c r="CX87" s="2"/>
       <x:c r="CY87" s="2"/>
       <x:c r="CZ87" s="2"/>
@@ -25015,13 +25169,13 @@
       <x:c r="AV88" s="2"/>
       <x:c r="AW88" s="2"/>
       <x:c r="AX88" s="2"/>
-      <x:c r="AY88" s="2" t="str">
+      <x:c r="AY88" s="2" t="str"/>
+      <x:c r="AZ88" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ88" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA88" s="2"/>
+      <x:c r="BA88" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB88" s="2"/>
       <x:c r="BC88" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -25037,7 +25191,9 @@
       <x:c r="BL88" s="2"/>
       <x:c r="BM88" s="2"/>
       <x:c r="BN88" s="2"/>
-      <x:c r="BO88" s="2"/>
+      <x:c r="BO88" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP88" s="2"/>
       <x:c r="BQ88" s="2"/>
       <x:c r="BR88" s="2" t="n">
@@ -25092,7 +25248,7 @@
       <x:c r="CT88" s="2"/>
       <x:c r="CU88" s="2"/>
       <x:c r="CV88" s="2"/>
-      <x:c r="CW88" s="2" t="str"/>
+      <x:c r="CW88" s="2"/>
       <x:c r="CX88" s="2"/>
       <x:c r="CY88" s="2"/>
       <x:c r="CZ88" s="2"/>
@@ -25297,13 +25453,13 @@
       <x:c r="AV89" s="2"/>
       <x:c r="AW89" s="2"/>
       <x:c r="AX89" s="2"/>
-      <x:c r="AY89" s="2" t="str">
+      <x:c r="AY89" s="2" t="str"/>
+      <x:c r="AZ89" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ89" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA89" s="2"/>
+      <x:c r="BA89" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB89" s="2"/>
       <x:c r="BC89" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -25319,7 +25475,9 @@
       <x:c r="BL89" s="2"/>
       <x:c r="BM89" s="2"/>
       <x:c r="BN89" s="2"/>
-      <x:c r="BO89" s="2"/>
+      <x:c r="BO89" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP89" s="2"/>
       <x:c r="BQ89" s="2"/>
       <x:c r="BR89" s="2" t="n">
@@ -25375,7 +25533,7 @@
       <x:c r="CT89" s="2"/>
       <x:c r="CU89" s="2"/>
       <x:c r="CV89" s="2"/>
-      <x:c r="CW89" s="2" t="str"/>
+      <x:c r="CW89" s="2"/>
       <x:c r="CX89" s="2"/>
       <x:c r="CY89" s="2"/>
       <x:c r="CZ89" s="2"/>
@@ -25580,13 +25738,13 @@
       <x:c r="AV90" s="2"/>
       <x:c r="AW90" s="2"/>
       <x:c r="AX90" s="2"/>
-      <x:c r="AY90" s="2" t="str">
+      <x:c r="AY90" s="2" t="str"/>
+      <x:c r="AZ90" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ90" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA90" s="2"/>
+      <x:c r="BA90" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB90" s="2"/>
       <x:c r="BC90" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -25602,7 +25760,9 @@
       <x:c r="BL90" s="2"/>
       <x:c r="BM90" s="2"/>
       <x:c r="BN90" s="2"/>
-      <x:c r="BO90" s="2"/>
+      <x:c r="BO90" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP90" s="2"/>
       <x:c r="BQ90" s="2"/>
       <x:c r="BR90" s="2" t="n">
@@ -25656,7 +25816,7 @@
       <x:c r="CT90" s="2"/>
       <x:c r="CU90" s="2"/>
       <x:c r="CV90" s="2"/>
-      <x:c r="CW90" s="2" t="str"/>
+      <x:c r="CW90" s="2"/>
       <x:c r="CX90" s="2"/>
       <x:c r="CY90" s="2"/>
       <x:c r="CZ90" s="2"/>
@@ -25861,13 +26021,13 @@
       <x:c r="AV91" s="2"/>
       <x:c r="AW91" s="2"/>
       <x:c r="AX91" s="2"/>
-      <x:c r="AY91" s="2" t="str">
+      <x:c r="AY91" s="2" t="str"/>
+      <x:c r="AZ91" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ91" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA91" s="2"/>
+      <x:c r="BA91" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB91" s="2"/>
       <x:c r="BC91" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -25883,7 +26043,9 @@
       <x:c r="BL91" s="2"/>
       <x:c r="BM91" s="2"/>
       <x:c r="BN91" s="2"/>
-      <x:c r="BO91" s="2"/>
+      <x:c r="BO91" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP91" s="2"/>
       <x:c r="BQ91" s="2"/>
       <x:c r="BR91" s="2" t="n">
@@ -25939,7 +26101,7 @@
       <x:c r="CT91" s="2"/>
       <x:c r="CU91" s="2"/>
       <x:c r="CV91" s="2"/>
-      <x:c r="CW91" s="2" t="str"/>
+      <x:c r="CW91" s="2"/>
       <x:c r="CX91" s="2"/>
       <x:c r="CY91" s="2"/>
       <x:c r="CZ91" s="2"/>
@@ -26144,13 +26306,13 @@
       <x:c r="AV92" s="2"/>
       <x:c r="AW92" s="2"/>
       <x:c r="AX92" s="2"/>
-      <x:c r="AY92" s="2" t="str">
+      <x:c r="AY92" s="2" t="str"/>
+      <x:c r="AZ92" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ92" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA92" s="2"/>
+      <x:c r="BA92" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB92" s="2"/>
       <x:c r="BC92" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -26166,7 +26328,9 @@
       <x:c r="BL92" s="2"/>
       <x:c r="BM92" s="2"/>
       <x:c r="BN92" s="2"/>
-      <x:c r="BO92" s="2"/>
+      <x:c r="BO92" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP92" s="2"/>
       <x:c r="BQ92" s="2"/>
       <x:c r="BR92" s="2" t="n">
@@ -26222,7 +26386,7 @@
       <x:c r="CT92" s="2"/>
       <x:c r="CU92" s="2"/>
       <x:c r="CV92" s="2"/>
-      <x:c r="CW92" s="2" t="str"/>
+      <x:c r="CW92" s="2"/>
       <x:c r="CX92" s="2"/>
       <x:c r="CY92" s="2"/>
       <x:c r="CZ92" s="2"/>
@@ -26427,13 +26591,13 @@
       <x:c r="AV93" s="2"/>
       <x:c r="AW93" s="2"/>
       <x:c r="AX93" s="2"/>
-      <x:c r="AY93" s="2" t="str">
+      <x:c r="AY93" s="2" t="str"/>
+      <x:c r="AZ93" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ93" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA93" s="2"/>
+      <x:c r="BA93" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB93" s="2"/>
       <x:c r="BC93" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -26449,7 +26613,9 @@
       <x:c r="BL93" s="2"/>
       <x:c r="BM93" s="2"/>
       <x:c r="BN93" s="2"/>
-      <x:c r="BO93" s="2"/>
+      <x:c r="BO93" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP93" s="2"/>
       <x:c r="BQ93" s="2"/>
       <x:c r="BR93" s="2" t="n">
@@ -26507,7 +26673,7 @@
       <x:c r="CT93" s="2"/>
       <x:c r="CU93" s="2"/>
       <x:c r="CV93" s="2"/>
-      <x:c r="CW93" s="2" t="str"/>
+      <x:c r="CW93" s="2"/>
       <x:c r="CX93" s="2"/>
       <x:c r="CY93" s="2"/>
       <x:c r="CZ93" s="2"/>
@@ -26712,13 +26878,13 @@
       <x:c r="AV94" s="2"/>
       <x:c r="AW94" s="2"/>
       <x:c r="AX94" s="2"/>
-      <x:c r="AY94" s="2" t="str">
+      <x:c r="AY94" s="2" t="str"/>
+      <x:c r="AZ94" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ94" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA94" s="2"/>
+      <x:c r="BA94" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB94" s="2"/>
       <x:c r="BC94" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -26734,7 +26900,9 @@
       <x:c r="BL94" s="2"/>
       <x:c r="BM94" s="2"/>
       <x:c r="BN94" s="2"/>
-      <x:c r="BO94" s="2"/>
+      <x:c r="BO94" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP94" s="2"/>
       <x:c r="BQ94" s="2"/>
       <x:c r="BR94" s="2" t="n">
@@ -26790,7 +26958,7 @@
       <x:c r="CT94" s="2"/>
       <x:c r="CU94" s="2"/>
       <x:c r="CV94" s="2"/>
-      <x:c r="CW94" s="2" t="str"/>
+      <x:c r="CW94" s="2"/>
       <x:c r="CX94" s="2"/>
       <x:c r="CY94" s="2"/>
       <x:c r="CZ94" s="2"/>
@@ -26995,13 +27163,13 @@
       <x:c r="AV95" s="2"/>
       <x:c r="AW95" s="2"/>
       <x:c r="AX95" s="2"/>
-      <x:c r="AY95" s="2" t="str">
+      <x:c r="AY95" s="2" t="str"/>
+      <x:c r="AZ95" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ95" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA95" s="2"/>
+      <x:c r="BA95" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB95" s="2"/>
       <x:c r="BC95" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -27017,7 +27185,9 @@
       <x:c r="BL95" s="2"/>
       <x:c r="BM95" s="2"/>
       <x:c r="BN95" s="2"/>
-      <x:c r="BO95" s="2"/>
+      <x:c r="BO95" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP95" s="2"/>
       <x:c r="BQ95" s="2"/>
       <x:c r="BR95" s="2" t="n">
@@ -27073,7 +27243,7 @@
       <x:c r="CT95" s="2"/>
       <x:c r="CU95" s="2"/>
       <x:c r="CV95" s="2"/>
-      <x:c r="CW95" s="2" t="str"/>
+      <x:c r="CW95" s="2"/>
       <x:c r="CX95" s="2"/>
       <x:c r="CY95" s="2"/>
       <x:c r="CZ95" s="2"/>
@@ -27278,13 +27448,13 @@
       <x:c r="AV96" s="2"/>
       <x:c r="AW96" s="2"/>
       <x:c r="AX96" s="2"/>
-      <x:c r="AY96" s="2" t="str">
+      <x:c r="AY96" s="2" t="str"/>
+      <x:c r="AZ96" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ96" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA96" s="2"/>
+      <x:c r="BA96" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB96" s="2"/>
       <x:c r="BC96" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -27300,7 +27470,9 @@
       <x:c r="BL96" s="2"/>
       <x:c r="BM96" s="2"/>
       <x:c r="BN96" s="2"/>
-      <x:c r="BO96" s="2"/>
+      <x:c r="BO96" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP96" s="2"/>
       <x:c r="BQ96" s="2"/>
       <x:c r="BR96" s="2" t="n">
@@ -27354,7 +27526,7 @@
       <x:c r="CT96" s="2"/>
       <x:c r="CU96" s="2"/>
       <x:c r="CV96" s="2"/>
-      <x:c r="CW96" s="2" t="str"/>
+      <x:c r="CW96" s="2"/>
       <x:c r="CX96" s="2"/>
       <x:c r="CY96" s="2"/>
       <x:c r="CZ96" s="2"/>
@@ -27559,13 +27731,13 @@
       <x:c r="AV97" s="2"/>
       <x:c r="AW97" s="2"/>
       <x:c r="AX97" s="2"/>
-      <x:c r="AY97" s="2" t="str">
+      <x:c r="AY97" s="2" t="str"/>
+      <x:c r="AZ97" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ97" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA97" s="2"/>
+      <x:c r="BA97" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB97" s="2"/>
       <x:c r="BC97" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -27581,7 +27753,9 @@
       <x:c r="BL97" s="2"/>
       <x:c r="BM97" s="2"/>
       <x:c r="BN97" s="2"/>
-      <x:c r="BO97" s="2"/>
+      <x:c r="BO97" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP97" s="2"/>
       <x:c r="BQ97" s="2"/>
       <x:c r="BR97" s="2" t="n">
@@ -27636,7 +27810,7 @@
       <x:c r="CT97" s="2"/>
       <x:c r="CU97" s="2"/>
       <x:c r="CV97" s="2"/>
-      <x:c r="CW97" s="2" t="str"/>
+      <x:c r="CW97" s="2"/>
       <x:c r="CX97" s="2"/>
       <x:c r="CY97" s="2"/>
       <x:c r="CZ97" s="2"/>
@@ -27841,13 +28015,13 @@
       <x:c r="AV98" s="2"/>
       <x:c r="AW98" s="2"/>
       <x:c r="AX98" s="2"/>
-      <x:c r="AY98" s="2" t="str">
+      <x:c r="AY98" s="2" t="str"/>
+      <x:c r="AZ98" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ98" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA98" s="2"/>
+      <x:c r="BA98" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB98" s="2"/>
       <x:c r="BC98" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -27863,7 +28037,9 @@
       <x:c r="BL98" s="2"/>
       <x:c r="BM98" s="2"/>
       <x:c r="BN98" s="2"/>
-      <x:c r="BO98" s="2"/>
+      <x:c r="BO98" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP98" s="2"/>
       <x:c r="BQ98" s="2"/>
       <x:c r="BR98" s="2" t="n">
@@ -27919,7 +28095,7 @@
       <x:c r="CT98" s="2"/>
       <x:c r="CU98" s="2"/>
       <x:c r="CV98" s="2"/>
-      <x:c r="CW98" s="2" t="str"/>
+      <x:c r="CW98" s="2"/>
       <x:c r="CX98" s="2"/>
       <x:c r="CY98" s="2"/>
       <x:c r="CZ98" s="2"/>
@@ -28124,13 +28300,13 @@
       <x:c r="AV99" s="2"/>
       <x:c r="AW99" s="2"/>
       <x:c r="AX99" s="2"/>
-      <x:c r="AY99" s="2" t="str">
+      <x:c r="AY99" s="2" t="str"/>
+      <x:c r="AZ99" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ99" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA99" s="2"/>
+      <x:c r="BA99" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB99" s="2"/>
       <x:c r="BC99" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -28146,7 +28322,9 @@
       <x:c r="BL99" s="2"/>
       <x:c r="BM99" s="2"/>
       <x:c r="BN99" s="2"/>
-      <x:c r="BO99" s="2"/>
+      <x:c r="BO99" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP99" s="2"/>
       <x:c r="BQ99" s="2"/>
       <x:c r="BR99" s="2" t="n">
@@ -28202,7 +28380,7 @@
       <x:c r="CT99" s="2"/>
       <x:c r="CU99" s="2"/>
       <x:c r="CV99" s="2"/>
-      <x:c r="CW99" s="2" t="str"/>
+      <x:c r="CW99" s="2"/>
       <x:c r="CX99" s="2"/>
       <x:c r="CY99" s="2"/>
       <x:c r="CZ99" s="2"/>
@@ -28407,13 +28585,13 @@
       <x:c r="AV100" s="2"/>
       <x:c r="AW100" s="2"/>
       <x:c r="AX100" s="2"/>
-      <x:c r="AY100" s="2" t="str">
+      <x:c r="AY100" s="2" t="str"/>
+      <x:c r="AZ100" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ100" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA100" s="2"/>
+      <x:c r="BA100" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB100" s="2"/>
       <x:c r="BC100" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -28429,7 +28607,9 @@
       <x:c r="BL100" s="2"/>
       <x:c r="BM100" s="2"/>
       <x:c r="BN100" s="2"/>
-      <x:c r="BO100" s="2"/>
+      <x:c r="BO100" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP100" s="2"/>
       <x:c r="BQ100" s="2"/>
       <x:c r="BR100" s="2" t="n">
@@ -28483,7 +28663,7 @@
       <x:c r="CT100" s="2"/>
       <x:c r="CU100" s="2"/>
       <x:c r="CV100" s="2"/>
-      <x:c r="CW100" s="2" t="str"/>
+      <x:c r="CW100" s="2"/>
       <x:c r="CX100" s="2"/>
       <x:c r="CY100" s="2"/>
       <x:c r="CZ100" s="2"/>
@@ -28688,13 +28868,13 @@
       <x:c r="AV101" s="2"/>
       <x:c r="AW101" s="2"/>
       <x:c r="AX101" s="2"/>
-      <x:c r="AY101" s="2" t="str">
+      <x:c r="AY101" s="2" t="str"/>
+      <x:c r="AZ101" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ101" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA101" s="2"/>
+      <x:c r="BA101" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB101" s="2"/>
       <x:c r="BC101" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -28710,7 +28890,9 @@
       <x:c r="BL101" s="2"/>
       <x:c r="BM101" s="2"/>
       <x:c r="BN101" s="2"/>
-      <x:c r="BO101" s="2"/>
+      <x:c r="BO101" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP101" s="2"/>
       <x:c r="BQ101" s="2"/>
       <x:c r="BR101" s="2" t="n">
@@ -28767,7 +28949,7 @@
       <x:c r="CT101" s="2"/>
       <x:c r="CU101" s="2"/>
       <x:c r="CV101" s="2"/>
-      <x:c r="CW101" s="2" t="str"/>
+      <x:c r="CW101" s="2"/>
       <x:c r="CX101" s="2"/>
       <x:c r="CY101" s="2"/>
       <x:c r="CZ101" s="2"/>
@@ -28972,13 +29154,13 @@
       <x:c r="AV102" s="2"/>
       <x:c r="AW102" s="2"/>
       <x:c r="AX102" s="2"/>
-      <x:c r="AY102" s="2" t="str">
+      <x:c r="AY102" s="2" t="str"/>
+      <x:c r="AZ102" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ102" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA102" s="2"/>
+      <x:c r="BA102" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB102" s="2"/>
       <x:c r="BC102" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -28994,7 +29176,9 @@
       <x:c r="BL102" s="2"/>
       <x:c r="BM102" s="2"/>
       <x:c r="BN102" s="2"/>
-      <x:c r="BO102" s="2"/>
+      <x:c r="BO102" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP102" s="2"/>
       <x:c r="BQ102" s="2"/>
       <x:c r="BR102" s="2" t="n">
@@ -29049,7 +29233,7 @@
       <x:c r="CT102" s="2"/>
       <x:c r="CU102" s="2"/>
       <x:c r="CV102" s="2"/>
-      <x:c r="CW102" s="2" t="str"/>
+      <x:c r="CW102" s="2"/>
       <x:c r="CX102" s="2"/>
       <x:c r="CY102" s="2"/>
       <x:c r="CZ102" s="2"/>
@@ -29254,13 +29438,13 @@
       <x:c r="AV103" s="2"/>
       <x:c r="AW103" s="2"/>
       <x:c r="AX103" s="2"/>
-      <x:c r="AY103" s="2" t="str">
+      <x:c r="AY103" s="2" t="str"/>
+      <x:c r="AZ103" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ103" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA103" s="2"/>
+      <x:c r="BA103" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB103" s="2"/>
       <x:c r="BC103" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -29276,7 +29460,9 @@
       <x:c r="BL103" s="2"/>
       <x:c r="BM103" s="2"/>
       <x:c r="BN103" s="2"/>
-      <x:c r="BO103" s="2"/>
+      <x:c r="BO103" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP103" s="2"/>
       <x:c r="BQ103" s="2"/>
       <x:c r="BR103" s="2" t="n">
@@ -29332,7 +29518,7 @@
       <x:c r="CT103" s="2"/>
       <x:c r="CU103" s="2"/>
       <x:c r="CV103" s="2"/>
-      <x:c r="CW103" s="2" t="str"/>
+      <x:c r="CW103" s="2"/>
       <x:c r="CX103" s="2"/>
       <x:c r="CY103" s="2"/>
       <x:c r="CZ103" s="2"/>
@@ -30031,13 +30217,13 @@
       <x:c r="AV106" s="2"/>
       <x:c r="AW106" s="2"/>
       <x:c r="AX106" s="2"/>
-      <x:c r="AY106" s="2" t="str">
+      <x:c r="AY106" s="2" t="str"/>
+      <x:c r="AZ106" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ106" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA106" s="2"/>
+      <x:c r="BA106" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB106" s="2"/>
       <x:c r="BC106" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -30053,7 +30239,9 @@
       <x:c r="BL106" s="2"/>
       <x:c r="BM106" s="2"/>
       <x:c r="BN106" s="2"/>
-      <x:c r="BO106" s="2"/>
+      <x:c r="BO106" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP106" s="2"/>
       <x:c r="BQ106" s="2"/>
       <x:c r="BR106" s="2" t="n">
@@ -30109,7 +30297,7 @@
       <x:c r="CT106" s="2"/>
       <x:c r="CU106" s="2"/>
       <x:c r="CV106" s="2"/>
-      <x:c r="CW106" s="2" t="str"/>
+      <x:c r="CW106" s="2"/>
       <x:c r="CX106" s="2"/>
       <x:c r="CY106" s="2"/>
       <x:c r="CZ106" s="2"/>
@@ -30314,13 +30502,13 @@
       <x:c r="AV107" s="2"/>
       <x:c r="AW107" s="2"/>
       <x:c r="AX107" s="2"/>
-      <x:c r="AY107" s="2" t="str">
+      <x:c r="AY107" s="2" t="str"/>
+      <x:c r="AZ107" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ107" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA107" s="2"/>
+      <x:c r="BA107" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB107" s="2"/>
       <x:c r="BC107" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -30336,7 +30524,9 @@
       <x:c r="BL107" s="2"/>
       <x:c r="BM107" s="2"/>
       <x:c r="BN107" s="2"/>
-      <x:c r="BO107" s="2"/>
+      <x:c r="BO107" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP107" s="2"/>
       <x:c r="BQ107" s="2"/>
       <x:c r="BR107" s="2" t="n">
@@ -30392,7 +30582,7 @@
       <x:c r="CT107" s="2"/>
       <x:c r="CU107" s="2"/>
       <x:c r="CV107" s="2"/>
-      <x:c r="CW107" s="2" t="str"/>
+      <x:c r="CW107" s="2"/>
       <x:c r="CX107" s="2"/>
       <x:c r="CY107" s="2"/>
       <x:c r="CZ107" s="2"/>
@@ -30597,13 +30787,13 @@
       <x:c r="AV108" s="2"/>
       <x:c r="AW108" s="2"/>
       <x:c r="AX108" s="2"/>
-      <x:c r="AY108" s="2" t="str">
+      <x:c r="AY108" s="2" t="str"/>
+      <x:c r="AZ108" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ108" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA108" s="2"/>
+      <x:c r="BA108" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB108" s="2"/>
       <x:c r="BC108" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -30619,7 +30809,9 @@
       <x:c r="BL108" s="2"/>
       <x:c r="BM108" s="2"/>
       <x:c r="BN108" s="2"/>
-      <x:c r="BO108" s="2"/>
+      <x:c r="BO108" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP108" s="2"/>
       <x:c r="BQ108" s="2"/>
       <x:c r="BR108" s="2" t="n">
@@ -30675,7 +30867,7 @@
       <x:c r="CT108" s="2"/>
       <x:c r="CU108" s="2"/>
       <x:c r="CV108" s="2"/>
-      <x:c r="CW108" s="2" t="str"/>
+      <x:c r="CW108" s="2"/>
       <x:c r="CX108" s="2"/>
       <x:c r="CY108" s="2"/>
       <x:c r="CZ108" s="2"/>
@@ -30880,13 +31072,13 @@
       <x:c r="AV109" s="2"/>
       <x:c r="AW109" s="2"/>
       <x:c r="AX109" s="2"/>
-      <x:c r="AY109" s="2" t="str">
+      <x:c r="AY109" s="2" t="str"/>
+      <x:c r="AZ109" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ109" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA109" s="2"/>
+      <x:c r="BA109" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB109" s="2"/>
       <x:c r="BC109" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -30902,7 +31094,9 @@
       <x:c r="BL109" s="2"/>
       <x:c r="BM109" s="2"/>
       <x:c r="BN109" s="2"/>
-      <x:c r="BO109" s="2"/>
+      <x:c r="BO109" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP109" s="2"/>
       <x:c r="BQ109" s="2"/>
       <x:c r="BR109" s="2" t="n">
@@ -30957,7 +31151,7 @@
       <x:c r="CT109" s="2"/>
       <x:c r="CU109" s="2"/>
       <x:c r="CV109" s="2"/>
-      <x:c r="CW109" s="2" t="str"/>
+      <x:c r="CW109" s="2"/>
       <x:c r="CX109" s="2"/>
       <x:c r="CY109" s="2"/>
       <x:c r="CZ109" s="2"/>
@@ -31162,13 +31356,13 @@
       <x:c r="AV110" s="2"/>
       <x:c r="AW110" s="2"/>
       <x:c r="AX110" s="2"/>
-      <x:c r="AY110" s="2" t="str">
+      <x:c r="AY110" s="2" t="str"/>
+      <x:c r="AZ110" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ110" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA110" s="2"/>
+      <x:c r="BA110" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB110" s="2"/>
       <x:c r="BC110" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -31184,7 +31378,9 @@
       <x:c r="BL110" s="2"/>
       <x:c r="BM110" s="2"/>
       <x:c r="BN110" s="2"/>
-      <x:c r="BO110" s="2"/>
+      <x:c r="BO110" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP110" s="2"/>
       <x:c r="BQ110" s="2"/>
       <x:c r="BR110" s="2" t="n">
@@ -31238,7 +31434,7 @@
       <x:c r="CT110" s="2"/>
       <x:c r="CU110" s="2"/>
       <x:c r="CV110" s="2"/>
-      <x:c r="CW110" s="2" t="str"/>
+      <x:c r="CW110" s="2"/>
       <x:c r="CX110" s="2"/>
       <x:c r="CY110" s="2"/>
       <x:c r="CZ110" s="2"/>
@@ -31443,13 +31639,13 @@
       <x:c r="AV111" s="2"/>
       <x:c r="AW111" s="2"/>
       <x:c r="AX111" s="2"/>
-      <x:c r="AY111" s="2" t="str">
+      <x:c r="AY111" s="2" t="str"/>
+      <x:c r="AZ111" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ111" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA111" s="2"/>
+      <x:c r="BA111" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB111" s="2"/>
       <x:c r="BC111" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -31465,7 +31661,9 @@
       <x:c r="BL111" s="2"/>
       <x:c r="BM111" s="2"/>
       <x:c r="BN111" s="2"/>
-      <x:c r="BO111" s="2"/>
+      <x:c r="BO111" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP111" s="2"/>
       <x:c r="BQ111" s="2"/>
       <x:c r="BR111" s="2" t="n">
@@ -31521,7 +31719,7 @@
       <x:c r="CT111" s="2"/>
       <x:c r="CU111" s="2"/>
       <x:c r="CV111" s="2"/>
-      <x:c r="CW111" s="2" t="str"/>
+      <x:c r="CW111" s="2"/>
       <x:c r="CX111" s="2"/>
       <x:c r="CY111" s="2"/>
       <x:c r="CZ111" s="2"/>
@@ -31726,13 +31924,13 @@
       <x:c r="AV112" s="2"/>
       <x:c r="AW112" s="2"/>
       <x:c r="AX112" s="2"/>
-      <x:c r="AY112" s="2" t="str">
+      <x:c r="AY112" s="2" t="str"/>
+      <x:c r="AZ112" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ112" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA112" s="2"/>
+      <x:c r="BA112" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB112" s="2"/>
       <x:c r="BC112" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -31748,7 +31946,9 @@
       <x:c r="BL112" s="2"/>
       <x:c r="BM112" s="2"/>
       <x:c r="BN112" s="2"/>
-      <x:c r="BO112" s="2"/>
+      <x:c r="BO112" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP112" s="2"/>
       <x:c r="BQ112" s="2"/>
       <x:c r="BR112" s="2" t="n">
@@ -31803,7 +32003,7 @@
       <x:c r="CT112" s="2"/>
       <x:c r="CU112" s="2"/>
       <x:c r="CV112" s="2"/>
-      <x:c r="CW112" s="2" t="str"/>
+      <x:c r="CW112" s="2"/>
       <x:c r="CX112" s="2"/>
       <x:c r="CY112" s="2"/>
       <x:c r="CZ112" s="2"/>
@@ -32255,13 +32455,13 @@
       <x:c r="AV114" s="2"/>
       <x:c r="AW114" s="2"/>
       <x:c r="AX114" s="2"/>
-      <x:c r="AY114" s="2" t="str">
+      <x:c r="AY114" s="2" t="str"/>
+      <x:c r="AZ114" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ114" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA114" s="2"/>
+      <x:c r="BA114" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB114" s="2"/>
       <x:c r="BC114" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -32277,7 +32477,9 @@
       <x:c r="BL114" s="2"/>
       <x:c r="BM114" s="2"/>
       <x:c r="BN114" s="2"/>
-      <x:c r="BO114" s="2"/>
+      <x:c r="BO114" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP114" s="2"/>
       <x:c r="BQ114" s="2"/>
       <x:c r="BR114" s="2" t="n">
@@ -32333,7 +32535,7 @@
       <x:c r="CT114" s="2"/>
       <x:c r="CU114" s="2"/>
       <x:c r="CV114" s="2"/>
-      <x:c r="CW114" s="2" t="str"/>
+      <x:c r="CW114" s="2"/>
       <x:c r="CX114" s="2"/>
       <x:c r="CY114" s="2"/>
       <x:c r="CZ114" s="2"/>
@@ -32538,13 +32740,13 @@
       <x:c r="AV115" s="2"/>
       <x:c r="AW115" s="2"/>
       <x:c r="AX115" s="2"/>
-      <x:c r="AY115" s="2" t="str">
+      <x:c r="AY115" s="2" t="str"/>
+      <x:c r="AZ115" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ115" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA115" s="2"/>
+      <x:c r="BA115" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB115" s="2"/>
       <x:c r="BC115" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -32560,7 +32762,9 @@
       <x:c r="BL115" s="2"/>
       <x:c r="BM115" s="2"/>
       <x:c r="BN115" s="2"/>
-      <x:c r="BO115" s="2"/>
+      <x:c r="BO115" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP115" s="2"/>
       <x:c r="BQ115" s="2"/>
       <x:c r="BR115" s="2" t="n">
@@ -32615,7 +32819,7 @@
       <x:c r="CT115" s="2"/>
       <x:c r="CU115" s="2"/>
       <x:c r="CV115" s="2"/>
-      <x:c r="CW115" s="2" t="str"/>
+      <x:c r="CW115" s="2"/>
       <x:c r="CX115" s="2"/>
       <x:c r="CY115" s="2"/>
       <x:c r="CZ115" s="2"/>
@@ -32820,13 +33024,13 @@
       <x:c r="AV116" s="2"/>
       <x:c r="AW116" s="2"/>
       <x:c r="AX116" s="2"/>
-      <x:c r="AY116" s="2" t="str">
+      <x:c r="AY116" s="2" t="str"/>
+      <x:c r="AZ116" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ116" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA116" s="2"/>
+      <x:c r="BA116" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB116" s="2"/>
       <x:c r="BC116" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -32842,7 +33046,9 @@
       <x:c r="BL116" s="2"/>
       <x:c r="BM116" s="2"/>
       <x:c r="BN116" s="2"/>
-      <x:c r="BO116" s="2"/>
+      <x:c r="BO116" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP116" s="2"/>
       <x:c r="BQ116" s="2"/>
       <x:c r="BR116" s="2" t="n">
@@ -32897,7 +33103,7 @@
       <x:c r="CT116" s="2"/>
       <x:c r="CU116" s="2"/>
       <x:c r="CV116" s="2"/>
-      <x:c r="CW116" s="2" t="str"/>
+      <x:c r="CW116" s="2"/>
       <x:c r="CX116" s="2"/>
       <x:c r="CY116" s="2"/>
       <x:c r="CZ116" s="2"/>
@@ -33596,13 +33802,13 @@
       <x:c r="AV119" s="2"/>
       <x:c r="AW119" s="2"/>
       <x:c r="AX119" s="2"/>
-      <x:c r="AY119" s="2" t="str">
+      <x:c r="AY119" s="2" t="str"/>
+      <x:c r="AZ119" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ119" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA119" s="2"/>
+      <x:c r="BA119" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB119" s="2"/>
       <x:c r="BC119" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -33618,7 +33824,9 @@
       <x:c r="BL119" s="2"/>
       <x:c r="BM119" s="2"/>
       <x:c r="BN119" s="2"/>
-      <x:c r="BO119" s="2"/>
+      <x:c r="BO119" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP119" s="2"/>
       <x:c r="BQ119" s="2"/>
       <x:c r="BR119" s="2" t="n">
@@ -33673,7 +33881,7 @@
       <x:c r="CT119" s="2"/>
       <x:c r="CU119" s="2"/>
       <x:c r="CV119" s="2"/>
-      <x:c r="CW119" s="2" t="str"/>
+      <x:c r="CW119" s="2"/>
       <x:c r="CX119" s="2"/>
       <x:c r="CY119" s="2"/>
       <x:c r="CZ119" s="2"/>
@@ -33878,13 +34086,13 @@
       <x:c r="AV120" s="2"/>
       <x:c r="AW120" s="2"/>
       <x:c r="AX120" s="2"/>
-      <x:c r="AY120" s="2" t="str">
+      <x:c r="AY120" s="2" t="str"/>
+      <x:c r="AZ120" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ120" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA120" s="2"/>
+      <x:c r="BA120" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB120" s="2"/>
       <x:c r="BC120" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -33900,7 +34108,9 @@
       <x:c r="BL120" s="2"/>
       <x:c r="BM120" s="2"/>
       <x:c r="BN120" s="2"/>
-      <x:c r="BO120" s="2"/>
+      <x:c r="BO120" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP120" s="2"/>
       <x:c r="BQ120" s="2"/>
       <x:c r="BR120" s="2" t="n">
@@ -33956,7 +34166,7 @@
       <x:c r="CT120" s="2"/>
       <x:c r="CU120" s="2"/>
       <x:c r="CV120" s="2"/>
-      <x:c r="CW120" s="2" t="str"/>
+      <x:c r="CW120" s="2"/>
       <x:c r="CX120" s="2"/>
       <x:c r="CY120" s="2"/>
       <x:c r="CZ120" s="2"/>
@@ -34161,13 +34371,13 @@
       <x:c r="AV121" s="2"/>
       <x:c r="AW121" s="2"/>
       <x:c r="AX121" s="2"/>
-      <x:c r="AY121" s="2" t="str">
+      <x:c r="AY121" s="2" t="str"/>
+      <x:c r="AZ121" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ121" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA121" s="2"/>
+      <x:c r="BA121" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB121" s="2"/>
       <x:c r="BC121" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -34183,7 +34393,9 @@
       <x:c r="BL121" s="2"/>
       <x:c r="BM121" s="2"/>
       <x:c r="BN121" s="2"/>
-      <x:c r="BO121" s="2"/>
+      <x:c r="BO121" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP121" s="2"/>
       <x:c r="BQ121" s="2"/>
       <x:c r="BR121" s="2" t="n">
@@ -34236,7 +34448,7 @@
       <x:c r="CT121" s="2"/>
       <x:c r="CU121" s="2"/>
       <x:c r="CV121" s="2"/>
-      <x:c r="CW121" s="2" t="str"/>
+      <x:c r="CW121" s="2"/>
       <x:c r="CX121" s="2"/>
       <x:c r="CY121" s="2"/>
       <x:c r="CZ121" s="2"/>
@@ -34441,13 +34653,13 @@
       <x:c r="AV122" s="2"/>
       <x:c r="AW122" s="2"/>
       <x:c r="AX122" s="2"/>
-      <x:c r="AY122" s="2" t="str">
+      <x:c r="AY122" s="2" t="str"/>
+      <x:c r="AZ122" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ122" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA122" s="2"/>
+      <x:c r="BA122" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB122" s="2"/>
       <x:c r="BC122" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -34463,7 +34675,9 @@
       <x:c r="BL122" s="2"/>
       <x:c r="BM122" s="2"/>
       <x:c r="BN122" s="2"/>
-      <x:c r="BO122" s="2"/>
+      <x:c r="BO122" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP122" s="2"/>
       <x:c r="BQ122" s="2"/>
       <x:c r="BR122" s="2" t="n">
@@ -34519,7 +34733,7 @@
       <x:c r="CT122" s="2"/>
       <x:c r="CU122" s="2"/>
       <x:c r="CV122" s="2"/>
-      <x:c r="CW122" s="2" t="str"/>
+      <x:c r="CW122" s="2"/>
       <x:c r="CX122" s="2"/>
       <x:c r="CY122" s="2"/>
       <x:c r="CZ122" s="2"/>
@@ -35218,13 +35432,13 @@
       <x:c r="AV125" s="2"/>
       <x:c r="AW125" s="2"/>
       <x:c r="AX125" s="2"/>
-      <x:c r="AY125" s="2" t="str">
+      <x:c r="AY125" s="2" t="str"/>
+      <x:c r="AZ125" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ125" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA125" s="2"/>
+      <x:c r="BA125" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB125" s="2"/>
       <x:c r="BC125" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -35240,7 +35454,9 @@
       <x:c r="BL125" s="2"/>
       <x:c r="BM125" s="2"/>
       <x:c r="BN125" s="2"/>
-      <x:c r="BO125" s="2"/>
+      <x:c r="BO125" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP125" s="2"/>
       <x:c r="BQ125" s="2"/>
       <x:c r="BR125" s="2" t="n">
@@ -35294,7 +35510,7 @@
       <x:c r="CT125" s="2"/>
       <x:c r="CU125" s="2"/>
       <x:c r="CV125" s="2"/>
-      <x:c r="CW125" s="2" t="str"/>
+      <x:c r="CW125" s="2"/>
       <x:c r="CX125" s="2"/>
       <x:c r="CY125" s="2"/>
       <x:c r="CZ125" s="2"/>
@@ -35499,13 +35715,13 @@
       <x:c r="AV126" s="2"/>
       <x:c r="AW126" s="2"/>
       <x:c r="AX126" s="2"/>
-      <x:c r="AY126" s="2" t="str">
+      <x:c r="AY126" s="2" t="str"/>
+      <x:c r="AZ126" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ126" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA126" s="2"/>
+      <x:c r="BA126" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB126" s="2"/>
       <x:c r="BC126" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -35521,7 +35737,9 @@
       <x:c r="BL126" s="2"/>
       <x:c r="BM126" s="2"/>
       <x:c r="BN126" s="2"/>
-      <x:c r="BO126" s="2"/>
+      <x:c r="BO126" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP126" s="2"/>
       <x:c r="BQ126" s="2"/>
       <x:c r="BR126" s="2" t="n">
@@ -35576,7 +35794,7 @@
       <x:c r="CT126" s="2"/>
       <x:c r="CU126" s="2"/>
       <x:c r="CV126" s="2"/>
-      <x:c r="CW126" s="2" t="str"/>
+      <x:c r="CW126" s="2"/>
       <x:c r="CX126" s="2"/>
       <x:c r="CY126" s="2"/>
       <x:c r="CZ126" s="2"/>
@@ -35781,13 +35999,13 @@
       <x:c r="AV127" s="2"/>
       <x:c r="AW127" s="2"/>
       <x:c r="AX127" s="2"/>
-      <x:c r="AY127" s="2" t="str">
+      <x:c r="AY127" s="2" t="str"/>
+      <x:c r="AZ127" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ127" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA127" s="2"/>
+      <x:c r="BA127" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB127" s="2"/>
       <x:c r="BC127" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -35803,7 +36021,9 @@
       <x:c r="BL127" s="2"/>
       <x:c r="BM127" s="2"/>
       <x:c r="BN127" s="2"/>
-      <x:c r="BO127" s="2"/>
+      <x:c r="BO127" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP127" s="2"/>
       <x:c r="BQ127" s="2"/>
       <x:c r="BR127" s="2" t="n">
@@ -35858,7 +36078,7 @@
       <x:c r="CT127" s="2"/>
       <x:c r="CU127" s="2"/>
       <x:c r="CV127" s="2"/>
-      <x:c r="CW127" s="2" t="str"/>
+      <x:c r="CW127" s="2"/>
       <x:c r="CX127" s="2"/>
       <x:c r="CY127" s="2"/>
       <x:c r="CZ127" s="2"/>
@@ -36063,13 +36283,13 @@
       <x:c r="AV128" s="2"/>
       <x:c r="AW128" s="2"/>
       <x:c r="AX128" s="2"/>
-      <x:c r="AY128" s="2" t="str">
+      <x:c r="AY128" s="2" t="str"/>
+      <x:c r="AZ128" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ128" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA128" s="2"/>
+      <x:c r="BA128" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB128" s="2"/>
       <x:c r="BC128" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -36085,7 +36305,9 @@
       <x:c r="BL128" s="2"/>
       <x:c r="BM128" s="2"/>
       <x:c r="BN128" s="2"/>
-      <x:c r="BO128" s="2"/>
+      <x:c r="BO128" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP128" s="2"/>
       <x:c r="BQ128" s="2"/>
       <x:c r="BR128" s="2" t="n">
@@ -36139,7 +36361,7 @@
       <x:c r="CT128" s="2"/>
       <x:c r="CU128" s="2"/>
       <x:c r="CV128" s="2"/>
-      <x:c r="CW128" s="2" t="str"/>
+      <x:c r="CW128" s="2"/>
       <x:c r="CX128" s="2"/>
       <x:c r="CY128" s="2"/>
       <x:c r="CZ128" s="2"/>
@@ -36344,13 +36566,13 @@
       <x:c r="AV129" s="2"/>
       <x:c r="AW129" s="2"/>
       <x:c r="AX129" s="2"/>
-      <x:c r="AY129" s="2" t="str">
+      <x:c r="AY129" s="2" t="str"/>
+      <x:c r="AZ129" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ129" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA129" s="2"/>
+      <x:c r="BA129" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB129" s="2"/>
       <x:c r="BC129" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -36366,7 +36588,9 @@
       <x:c r="BL129" s="2"/>
       <x:c r="BM129" s="2"/>
       <x:c r="BN129" s="2"/>
-      <x:c r="BO129" s="2"/>
+      <x:c r="BO129" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP129" s="2"/>
       <x:c r="BQ129" s="2"/>
       <x:c r="BR129" s="2" t="n">
@@ -36422,7 +36646,7 @@
       <x:c r="CT129" s="2"/>
       <x:c r="CU129" s="2"/>
       <x:c r="CV129" s="2"/>
-      <x:c r="CW129" s="2" t="str"/>
+      <x:c r="CW129" s="2"/>
       <x:c r="CX129" s="2"/>
       <x:c r="CY129" s="2"/>
       <x:c r="CZ129" s="2"/>
@@ -36627,13 +36851,13 @@
       <x:c r="AV130" s="2"/>
       <x:c r="AW130" s="2"/>
       <x:c r="AX130" s="2"/>
-      <x:c r="AY130" s="2" t="str">
+      <x:c r="AY130" s="2" t="str"/>
+      <x:c r="AZ130" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ130" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA130" s="2"/>
+      <x:c r="BA130" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB130" s="2"/>
       <x:c r="BC130" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -36649,7 +36873,9 @@
       <x:c r="BL130" s="2"/>
       <x:c r="BM130" s="2"/>
       <x:c r="BN130" s="2"/>
-      <x:c r="BO130" s="2"/>
+      <x:c r="BO130" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP130" s="2"/>
       <x:c r="BQ130" s="2"/>
       <x:c r="BR130" s="2" t="n">
@@ -36705,7 +36931,7 @@
       <x:c r="CT130" s="2"/>
       <x:c r="CU130" s="2"/>
       <x:c r="CV130" s="2"/>
-      <x:c r="CW130" s="2" t="str"/>
+      <x:c r="CW130" s="2"/>
       <x:c r="CX130" s="2"/>
       <x:c r="CY130" s="2"/>
       <x:c r="CZ130" s="2"/>
@@ -37157,13 +37383,13 @@
       <x:c r="AV132" s="2"/>
       <x:c r="AW132" s="2"/>
       <x:c r="AX132" s="2"/>
-      <x:c r="AY132" s="2" t="str">
+      <x:c r="AY132" s="2" t="str"/>
+      <x:c r="AZ132" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ132" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA132" s="2"/>
+      <x:c r="BA132" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB132" s="2"/>
       <x:c r="BC132" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -37179,7 +37405,9 @@
       <x:c r="BL132" s="2"/>
       <x:c r="BM132" s="2"/>
       <x:c r="BN132" s="2"/>
-      <x:c r="BO132" s="2"/>
+      <x:c r="BO132" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP132" s="2"/>
       <x:c r="BQ132" s="2"/>
       <x:c r="BR132" s="2" t="n">
@@ -37235,7 +37463,7 @@
       <x:c r="CT132" s="2"/>
       <x:c r="CU132" s="2"/>
       <x:c r="CV132" s="2"/>
-      <x:c r="CW132" s="2" t="str"/>
+      <x:c r="CW132" s="2"/>
       <x:c r="CX132" s="2"/>
       <x:c r="CY132" s="2"/>
       <x:c r="CZ132" s="2"/>
@@ -37440,13 +37668,13 @@
       <x:c r="AV133" s="2"/>
       <x:c r="AW133" s="2"/>
       <x:c r="AX133" s="2"/>
-      <x:c r="AY133" s="2" t="str">
+      <x:c r="AY133" s="2" t="str"/>
+      <x:c r="AZ133" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ133" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA133" s="2"/>
+      <x:c r="BA133" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB133" s="2"/>
       <x:c r="BC133" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -37462,7 +37690,9 @@
       <x:c r="BL133" s="2"/>
       <x:c r="BM133" s="2"/>
       <x:c r="BN133" s="2"/>
-      <x:c r="BO133" s="2"/>
+      <x:c r="BO133" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP133" s="2"/>
       <x:c r="BQ133" s="2"/>
       <x:c r="BR133" s="2" t="n">
@@ -37517,7 +37747,7 @@
       <x:c r="CT133" s="2"/>
       <x:c r="CU133" s="2"/>
       <x:c r="CV133" s="2"/>
-      <x:c r="CW133" s="2" t="str"/>
+      <x:c r="CW133" s="2"/>
       <x:c r="CX133" s="2"/>
       <x:c r="CY133" s="2"/>
       <x:c r="CZ133" s="2"/>
@@ -37722,13 +37952,13 @@
       <x:c r="AV134" s="2"/>
       <x:c r="AW134" s="2"/>
       <x:c r="AX134" s="2"/>
-      <x:c r="AY134" s="2" t="str">
+      <x:c r="AY134" s="2" t="str"/>
+      <x:c r="AZ134" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ134" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA134" s="2"/>
+      <x:c r="BA134" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB134" s="2"/>
       <x:c r="BC134" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -37744,7 +37974,9 @@
       <x:c r="BL134" s="2"/>
       <x:c r="BM134" s="2"/>
       <x:c r="BN134" s="2"/>
-      <x:c r="BO134" s="2"/>
+      <x:c r="BO134" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP134" s="2"/>
       <x:c r="BQ134" s="2"/>
       <x:c r="BR134" s="2" t="n">
@@ -37799,7 +38031,7 @@
       <x:c r="CT134" s="2"/>
       <x:c r="CU134" s="2"/>
       <x:c r="CV134" s="2"/>
-      <x:c r="CW134" s="2" t="str"/>
+      <x:c r="CW134" s="2"/>
       <x:c r="CX134" s="2"/>
       <x:c r="CY134" s="2"/>
       <x:c r="CZ134" s="2"/>
@@ -38004,13 +38236,13 @@
       <x:c r="AV135" s="2"/>
       <x:c r="AW135" s="2"/>
       <x:c r="AX135" s="2"/>
-      <x:c r="AY135" s="2" t="str">
+      <x:c r="AY135" s="2" t="str"/>
+      <x:c r="AZ135" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ135" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA135" s="2"/>
+      <x:c r="BA135" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB135" s="2"/>
       <x:c r="BC135" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -38026,7 +38258,9 @@
       <x:c r="BL135" s="2"/>
       <x:c r="BM135" s="2"/>
       <x:c r="BN135" s="2"/>
-      <x:c r="BO135" s="2"/>
+      <x:c r="BO135" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP135" s="2"/>
       <x:c r="BQ135" s="2"/>
       <x:c r="BR135" s="2" t="n">
@@ -38082,7 +38316,7 @@
       <x:c r="CT135" s="2"/>
       <x:c r="CU135" s="2"/>
       <x:c r="CV135" s="2"/>
-      <x:c r="CW135" s="2" t="str"/>
+      <x:c r="CW135" s="2"/>
       <x:c r="CX135" s="2"/>
       <x:c r="CY135" s="2"/>
       <x:c r="CZ135" s="2"/>
@@ -38287,13 +38521,13 @@
       <x:c r="AV136" s="2"/>
       <x:c r="AW136" s="2"/>
       <x:c r="AX136" s="2"/>
-      <x:c r="AY136" s="2" t="str">
+      <x:c r="AY136" s="2" t="str"/>
+      <x:c r="AZ136" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ136" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA136" s="2"/>
+      <x:c r="BA136" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB136" s="2"/>
       <x:c r="BC136" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -38309,7 +38543,9 @@
       <x:c r="BL136" s="2"/>
       <x:c r="BM136" s="2"/>
       <x:c r="BN136" s="2"/>
-      <x:c r="BO136" s="2"/>
+      <x:c r="BO136" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP136" s="2"/>
       <x:c r="BQ136" s="2"/>
       <x:c r="BR136" s="2" t="n">
@@ -38363,7 +38599,7 @@
       <x:c r="CT136" s="2"/>
       <x:c r="CU136" s="2"/>
       <x:c r="CV136" s="2"/>
-      <x:c r="CW136" s="2" t="str"/>
+      <x:c r="CW136" s="2"/>
       <x:c r="CX136" s="2"/>
       <x:c r="CY136" s="2"/>
       <x:c r="CZ136" s="2"/>
@@ -38568,13 +38804,13 @@
       <x:c r="AV137" s="2"/>
       <x:c r="AW137" s="2"/>
       <x:c r="AX137" s="2"/>
-      <x:c r="AY137" s="2" t="str">
+      <x:c r="AY137" s="2" t="str"/>
+      <x:c r="AZ137" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ137" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA137" s="2"/>
+      <x:c r="BA137" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB137" s="2"/>
       <x:c r="BC137" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -38590,7 +38826,9 @@
       <x:c r="BL137" s="2"/>
       <x:c r="BM137" s="2"/>
       <x:c r="BN137" s="2"/>
-      <x:c r="BO137" s="2"/>
+      <x:c r="BO137" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP137" s="2"/>
       <x:c r="BQ137" s="2"/>
       <x:c r="BR137" s="2" t="n">
@@ -38646,7 +38884,7 @@
       <x:c r="CT137" s="2"/>
       <x:c r="CU137" s="2"/>
       <x:c r="CV137" s="2"/>
-      <x:c r="CW137" s="2" t="str"/>
+      <x:c r="CW137" s="2"/>
       <x:c r="CX137" s="2"/>
       <x:c r="CY137" s="2"/>
       <x:c r="CZ137" s="2"/>
@@ -38851,13 +39089,13 @@
       <x:c r="AV138" s="2"/>
       <x:c r="AW138" s="2"/>
       <x:c r="AX138" s="2"/>
-      <x:c r="AY138" s="2" t="str">
+      <x:c r="AY138" s="2" t="str"/>
+      <x:c r="AZ138" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ138" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA138" s="2"/>
+      <x:c r="BA138" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB138" s="2"/>
       <x:c r="BC138" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -38873,7 +39111,9 @@
       <x:c r="BL138" s="2"/>
       <x:c r="BM138" s="2"/>
       <x:c r="BN138" s="2"/>
-      <x:c r="BO138" s="2"/>
+      <x:c r="BO138" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP138" s="2"/>
       <x:c r="BQ138" s="2"/>
       <x:c r="BR138" s="2" t="n">
@@ -38929,7 +39169,7 @@
       <x:c r="CT138" s="2"/>
       <x:c r="CU138" s="2"/>
       <x:c r="CV138" s="2"/>
-      <x:c r="CW138" s="2" t="str"/>
+      <x:c r="CW138" s="2"/>
       <x:c r="CX138" s="2"/>
       <x:c r="CY138" s="2"/>
       <x:c r="CZ138" s="2"/>
@@ -39134,13 +39374,13 @@
       <x:c r="AV139" s="2"/>
       <x:c r="AW139" s="2"/>
       <x:c r="AX139" s="2"/>
-      <x:c r="AY139" s="2" t="str">
+      <x:c r="AY139" s="2" t="str"/>
+      <x:c r="AZ139" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ139" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA139" s="2"/>
+      <x:c r="BA139" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB139" s="2"/>
       <x:c r="BC139" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -39156,7 +39396,9 @@
       <x:c r="BL139" s="2"/>
       <x:c r="BM139" s="2"/>
       <x:c r="BN139" s="2"/>
-      <x:c r="BO139" s="2"/>
+      <x:c r="BO139" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP139" s="2"/>
       <x:c r="BQ139" s="2"/>
       <x:c r="BR139" s="2" t="n">
@@ -39213,7 +39455,7 @@
       <x:c r="CT139" s="2"/>
       <x:c r="CU139" s="2"/>
       <x:c r="CV139" s="2"/>
-      <x:c r="CW139" s="2" t="str"/>
+      <x:c r="CW139" s="2"/>
       <x:c r="CX139" s="2"/>
       <x:c r="CY139" s="2"/>
       <x:c r="CZ139" s="2"/>
@@ -39418,13 +39660,13 @@
       <x:c r="AV140" s="2"/>
       <x:c r="AW140" s="2"/>
       <x:c r="AX140" s="2"/>
-      <x:c r="AY140" s="2" t="str">
+      <x:c r="AY140" s="2" t="str"/>
+      <x:c r="AZ140" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ140" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA140" s="2"/>
+      <x:c r="BA140" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB140" s="2"/>
       <x:c r="BC140" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -39440,7 +39682,9 @@
       <x:c r="BL140" s="2"/>
       <x:c r="BM140" s="2"/>
       <x:c r="BN140" s="2"/>
-      <x:c r="BO140" s="2"/>
+      <x:c r="BO140" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP140" s="2"/>
       <x:c r="BQ140" s="2"/>
       <x:c r="BR140" s="2" t="n">
@@ -39494,7 +39738,7 @@
       <x:c r="CT140" s="2"/>
       <x:c r="CU140" s="2"/>
       <x:c r="CV140" s="2"/>
-      <x:c r="CW140" s="2" t="str"/>
+      <x:c r="CW140" s="2"/>
       <x:c r="CX140" s="2"/>
       <x:c r="CY140" s="2"/>
       <x:c r="CZ140" s="2"/>
@@ -39699,13 +39943,13 @@
       <x:c r="AV141" s="2"/>
       <x:c r="AW141" s="2"/>
       <x:c r="AX141" s="2"/>
-      <x:c r="AY141" s="2" t="str">
+      <x:c r="AY141" s="2" t="str"/>
+      <x:c r="AZ141" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ141" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA141" s="2"/>
+      <x:c r="BA141" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB141" s="2"/>
       <x:c r="BC141" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -39721,7 +39965,9 @@
       <x:c r="BL141" s="2"/>
       <x:c r="BM141" s="2"/>
       <x:c r="BN141" s="2"/>
-      <x:c r="BO141" s="2"/>
+      <x:c r="BO141" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP141" s="2"/>
       <x:c r="BQ141" s="2"/>
       <x:c r="BR141" s="2" t="n">
@@ -39775,7 +40021,7 @@
       <x:c r="CT141" s="2"/>
       <x:c r="CU141" s="2"/>
       <x:c r="CV141" s="2"/>
-      <x:c r="CW141" s="2" t="str"/>
+      <x:c r="CW141" s="2"/>
       <x:c r="CX141" s="2"/>
       <x:c r="CY141" s="2"/>
       <x:c r="CZ141" s="2"/>
@@ -39980,13 +40226,13 @@
       <x:c r="AV142" s="2"/>
       <x:c r="AW142" s="2"/>
       <x:c r="AX142" s="2"/>
-      <x:c r="AY142" s="2" t="str">
+      <x:c r="AY142" s="2" t="str"/>
+      <x:c r="AZ142" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ142" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA142" s="2"/>
+      <x:c r="BA142" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB142" s="2"/>
       <x:c r="BC142" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -40002,7 +40248,9 @@
       <x:c r="BL142" s="2"/>
       <x:c r="BM142" s="2"/>
       <x:c r="BN142" s="2"/>
-      <x:c r="BO142" s="2"/>
+      <x:c r="BO142" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP142" s="2"/>
       <x:c r="BQ142" s="2"/>
       <x:c r="BR142" s="2" t="n">
@@ -40056,7 +40304,7 @@
       <x:c r="CT142" s="2"/>
       <x:c r="CU142" s="2"/>
       <x:c r="CV142" s="2"/>
-      <x:c r="CW142" s="2" t="str"/>
+      <x:c r="CW142" s="2"/>
       <x:c r="CX142" s="2"/>
       <x:c r="CY142" s="2"/>
       <x:c r="CZ142" s="2"/>
@@ -40261,13 +40509,13 @@
       <x:c r="AV143" s="2"/>
       <x:c r="AW143" s="2"/>
       <x:c r="AX143" s="2"/>
-      <x:c r="AY143" s="2" t="str">
+      <x:c r="AY143" s="2" t="str"/>
+      <x:c r="AZ143" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ143" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA143" s="2"/>
+      <x:c r="BA143" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB143" s="2"/>
       <x:c r="BC143" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -40283,7 +40531,9 @@
       <x:c r="BL143" s="2"/>
       <x:c r="BM143" s="2"/>
       <x:c r="BN143" s="2"/>
-      <x:c r="BO143" s="2"/>
+      <x:c r="BO143" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP143" s="2"/>
       <x:c r="BQ143" s="2"/>
       <x:c r="BR143" s="2" t="n">
@@ -40337,7 +40587,7 @@
       <x:c r="CT143" s="2"/>
       <x:c r="CU143" s="2"/>
       <x:c r="CV143" s="2"/>
-      <x:c r="CW143" s="2" t="str"/>
+      <x:c r="CW143" s="2"/>
       <x:c r="CX143" s="2"/>
       <x:c r="CY143" s="2"/>
       <x:c r="CZ143" s="2"/>
@@ -40542,13 +40792,13 @@
       <x:c r="AV144" s="2"/>
       <x:c r="AW144" s="2"/>
       <x:c r="AX144" s="2"/>
-      <x:c r="AY144" s="2" t="str">
+      <x:c r="AY144" s="2" t="str"/>
+      <x:c r="AZ144" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ144" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA144" s="2"/>
+      <x:c r="BA144" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB144" s="2"/>
       <x:c r="BC144" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -40564,7 +40814,9 @@
       <x:c r="BL144" s="2"/>
       <x:c r="BM144" s="2"/>
       <x:c r="BN144" s="2"/>
-      <x:c r="BO144" s="2"/>
+      <x:c r="BO144" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP144" s="2"/>
       <x:c r="BQ144" s="2"/>
       <x:c r="BR144" s="2" t="n">
@@ -40618,7 +40870,7 @@
       <x:c r="CT144" s="2"/>
       <x:c r="CU144" s="2"/>
       <x:c r="CV144" s="2"/>
-      <x:c r="CW144" s="2" t="str"/>
+      <x:c r="CW144" s="2"/>
       <x:c r="CX144" s="2"/>
       <x:c r="CY144" s="2"/>
       <x:c r="CZ144" s="2"/>
@@ -40823,13 +41075,13 @@
       <x:c r="AV145" s="2"/>
       <x:c r="AW145" s="2"/>
       <x:c r="AX145" s="2"/>
-      <x:c r="AY145" s="2" t="str">
+      <x:c r="AY145" s="2" t="str"/>
+      <x:c r="AZ145" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ145" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA145" s="2"/>
+      <x:c r="BA145" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB145" s="2"/>
       <x:c r="BC145" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -40845,7 +41097,9 @@
       <x:c r="BL145" s="2"/>
       <x:c r="BM145" s="2"/>
       <x:c r="BN145" s="2"/>
-      <x:c r="BO145" s="2"/>
+      <x:c r="BO145" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP145" s="2"/>
       <x:c r="BQ145" s="2"/>
       <x:c r="BR145" s="2" t="n">
@@ -40900,7 +41154,7 @@
       <x:c r="CT145" s="2"/>
       <x:c r="CU145" s="2"/>
       <x:c r="CV145" s="2"/>
-      <x:c r="CW145" s="2" t="str"/>
+      <x:c r="CW145" s="2"/>
       <x:c r="CX145" s="2"/>
       <x:c r="CY145" s="2"/>
       <x:c r="CZ145" s="2"/>
@@ -41105,13 +41359,13 @@
       <x:c r="AV146" s="2"/>
       <x:c r="AW146" s="2"/>
       <x:c r="AX146" s="2"/>
-      <x:c r="AY146" s="2" t="str">
+      <x:c r="AY146" s="2" t="str"/>
+      <x:c r="AZ146" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ146" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA146" s="2"/>
+      <x:c r="BA146" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB146" s="2"/>
       <x:c r="BC146" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -41127,7 +41381,9 @@
       <x:c r="BL146" s="2"/>
       <x:c r="BM146" s="2"/>
       <x:c r="BN146" s="2"/>
-      <x:c r="BO146" s="2"/>
+      <x:c r="BO146" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP146" s="2"/>
       <x:c r="BQ146" s="2"/>
       <x:c r="BR146" s="2" t="n">
@@ -41183,7 +41439,7 @@
       <x:c r="CT146" s="2"/>
       <x:c r="CU146" s="2"/>
       <x:c r="CV146" s="2"/>
-      <x:c r="CW146" s="2" t="str"/>
+      <x:c r="CW146" s="2"/>
       <x:c r="CX146" s="2"/>
       <x:c r="CY146" s="2"/>
       <x:c r="CZ146" s="2"/>
@@ -41882,13 +42138,13 @@
       <x:c r="AV149" s="2"/>
       <x:c r="AW149" s="2"/>
       <x:c r="AX149" s="2"/>
-      <x:c r="AY149" s="2" t="str">
+      <x:c r="AY149" s="2" t="str"/>
+      <x:c r="AZ149" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ149" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA149" s="2"/>
+      <x:c r="BA149" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB149" s="2"/>
       <x:c r="BC149" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -41904,7 +42160,9 @@
       <x:c r="BL149" s="2"/>
       <x:c r="BM149" s="2"/>
       <x:c r="BN149" s="2"/>
-      <x:c r="BO149" s="2"/>
+      <x:c r="BO149" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP149" s="2"/>
       <x:c r="BQ149" s="2"/>
       <x:c r="BR149" s="2" t="n">
@@ -41960,7 +42218,7 @@
       <x:c r="CT149" s="2"/>
       <x:c r="CU149" s="2"/>
       <x:c r="CV149" s="2"/>
-      <x:c r="CW149" s="2" t="str"/>
+      <x:c r="CW149" s="2"/>
       <x:c r="CX149" s="2"/>
       <x:c r="CY149" s="2"/>
       <x:c r="CZ149" s="2"/>
@@ -42165,13 +42423,13 @@
       <x:c r="AV150" s="2"/>
       <x:c r="AW150" s="2"/>
       <x:c r="AX150" s="2"/>
-      <x:c r="AY150" s="2" t="str">
+      <x:c r="AY150" s="2" t="str"/>
+      <x:c r="AZ150" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ150" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA150" s="2"/>
+      <x:c r="BA150" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB150" s="2"/>
       <x:c r="BC150" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -42187,7 +42445,9 @@
       <x:c r="BL150" s="2"/>
       <x:c r="BM150" s="2"/>
       <x:c r="BN150" s="2"/>
-      <x:c r="BO150" s="2"/>
+      <x:c r="BO150" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP150" s="2"/>
       <x:c r="BQ150" s="2"/>
       <x:c r="BR150" s="2" t="n">
@@ -42245,7 +42505,7 @@
       <x:c r="CT150" s="2"/>
       <x:c r="CU150" s="2"/>
       <x:c r="CV150" s="2"/>
-      <x:c r="CW150" s="2" t="str"/>
+      <x:c r="CW150" s="2"/>
       <x:c r="CX150" s="2"/>
       <x:c r="CY150" s="2"/>
       <x:c r="CZ150" s="2"/>
@@ -42450,13 +42710,13 @@
       <x:c r="AV151" s="2"/>
       <x:c r="AW151" s="2"/>
       <x:c r="AX151" s="2"/>
-      <x:c r="AY151" s="2" t="str">
+      <x:c r="AY151" s="2" t="str"/>
+      <x:c r="AZ151" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ151" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA151" s="2"/>
+      <x:c r="BA151" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB151" s="2"/>
       <x:c r="BC151" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -42472,7 +42732,9 @@
       <x:c r="BL151" s="2"/>
       <x:c r="BM151" s="2"/>
       <x:c r="BN151" s="2"/>
-      <x:c r="BO151" s="2"/>
+      <x:c r="BO151" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP151" s="2"/>
       <x:c r="BQ151" s="2"/>
       <x:c r="BR151" s="2" t="n">
@@ -42530,7 +42792,7 @@
       <x:c r="CT151" s="2"/>
       <x:c r="CU151" s="2"/>
       <x:c r="CV151" s="2"/>
-      <x:c r="CW151" s="2" t="str"/>
+      <x:c r="CW151" s="2"/>
       <x:c r="CX151" s="2"/>
       <x:c r="CY151" s="2"/>
       <x:c r="CZ151" s="2"/>
@@ -42735,13 +42997,13 @@
       <x:c r="AV152" s="2"/>
       <x:c r="AW152" s="2"/>
       <x:c r="AX152" s="2"/>
-      <x:c r="AY152" s="2" t="str">
+      <x:c r="AY152" s="2" t="str"/>
+      <x:c r="AZ152" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ152" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA152" s="2"/>
+      <x:c r="BA152" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB152" s="2"/>
       <x:c r="BC152" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -42757,7 +43019,9 @@
       <x:c r="BL152" s="2"/>
       <x:c r="BM152" s="2"/>
       <x:c r="BN152" s="2"/>
-      <x:c r="BO152" s="2"/>
+      <x:c r="BO152" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP152" s="2"/>
       <x:c r="BQ152" s="2"/>
       <x:c r="BR152" s="2" t="n">
@@ -42815,7 +43079,7 @@
       <x:c r="CT152" s="2"/>
       <x:c r="CU152" s="2"/>
       <x:c r="CV152" s="2"/>
-      <x:c r="CW152" s="2" t="str"/>
+      <x:c r="CW152" s="2"/>
       <x:c r="CX152" s="2"/>
       <x:c r="CY152" s="2"/>
       <x:c r="CZ152" s="2"/>
@@ -43020,13 +43284,13 @@
       <x:c r="AV153" s="2"/>
       <x:c r="AW153" s="2"/>
       <x:c r="AX153" s="2"/>
-      <x:c r="AY153" s="2" t="str">
+      <x:c r="AY153" s="2" t="str"/>
+      <x:c r="AZ153" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ153" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA153" s="2"/>
+      <x:c r="BA153" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB153" s="2"/>
       <x:c r="BC153" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -43042,7 +43306,9 @@
       <x:c r="BL153" s="2"/>
       <x:c r="BM153" s="2"/>
       <x:c r="BN153" s="2"/>
-      <x:c r="BO153" s="2"/>
+      <x:c r="BO153" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP153" s="2"/>
       <x:c r="BQ153" s="2"/>
       <x:c r="BR153" s="2" t="n">
@@ -43099,7 +43365,7 @@
       <x:c r="CT153" s="2"/>
       <x:c r="CU153" s="2"/>
       <x:c r="CV153" s="2"/>
-      <x:c r="CW153" s="2" t="str"/>
+      <x:c r="CW153" s="2"/>
       <x:c r="CX153" s="2"/>
       <x:c r="CY153" s="2"/>
       <x:c r="CZ153" s="2"/>
@@ -43304,13 +43570,13 @@
       <x:c r="AV154" s="2"/>
       <x:c r="AW154" s="2"/>
       <x:c r="AX154" s="2"/>
-      <x:c r="AY154" s="2" t="str">
+      <x:c r="AY154" s="2" t="str"/>
+      <x:c r="AZ154" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ154" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA154" s="2"/>
+      <x:c r="BA154" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB154" s="2"/>
       <x:c r="BC154" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -43326,7 +43592,9 @@
       <x:c r="BL154" s="2"/>
       <x:c r="BM154" s="2"/>
       <x:c r="BN154" s="2"/>
-      <x:c r="BO154" s="2"/>
+      <x:c r="BO154" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP154" s="2"/>
       <x:c r="BQ154" s="2"/>
       <x:c r="BR154" s="2" t="n">
@@ -43382,7 +43650,7 @@
       <x:c r="CT154" s="2"/>
       <x:c r="CU154" s="2"/>
       <x:c r="CV154" s="2"/>
-      <x:c r="CW154" s="2" t="str"/>
+      <x:c r="CW154" s="2"/>
       <x:c r="CX154" s="2"/>
       <x:c r="CY154" s="2"/>
       <x:c r="CZ154" s="2"/>
@@ -43587,13 +43855,13 @@
       <x:c r="AV155" s="2"/>
       <x:c r="AW155" s="2"/>
       <x:c r="AX155" s="2"/>
-      <x:c r="AY155" s="2" t="str">
+      <x:c r="AY155" s="2" t="str"/>
+      <x:c r="AZ155" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ155" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA155" s="2"/>
+      <x:c r="BA155" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB155" s="2"/>
       <x:c r="BC155" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -43609,7 +43877,9 @@
       <x:c r="BL155" s="2"/>
       <x:c r="BM155" s="2"/>
       <x:c r="BN155" s="2"/>
-      <x:c r="BO155" s="2"/>
+      <x:c r="BO155" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP155" s="2"/>
       <x:c r="BQ155" s="2"/>
       <x:c r="BR155" s="2" t="n">
@@ -43668,7 +43938,7 @@
       <x:c r="CT155" s="2"/>
       <x:c r="CU155" s="2"/>
       <x:c r="CV155" s="2"/>
-      <x:c r="CW155" s="2" t="str"/>
+      <x:c r="CW155" s="2"/>
       <x:c r="CX155" s="2"/>
       <x:c r="CY155" s="2"/>
       <x:c r="CZ155" s="2"/>
@@ -43873,13 +44143,13 @@
       <x:c r="AV156" s="2"/>
       <x:c r="AW156" s="2"/>
       <x:c r="AX156" s="2"/>
-      <x:c r="AY156" s="2" t="str">
+      <x:c r="AY156" s="2" t="str"/>
+      <x:c r="AZ156" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ156" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA156" s="2"/>
+      <x:c r="BA156" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB156" s="2"/>
       <x:c r="BC156" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -43895,7 +44165,9 @@
       <x:c r="BL156" s="2"/>
       <x:c r="BM156" s="2"/>
       <x:c r="BN156" s="2"/>
-      <x:c r="BO156" s="2"/>
+      <x:c r="BO156" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP156" s="2"/>
       <x:c r="BQ156" s="2"/>
       <x:c r="BR156" s="2" t="n">
@@ -43954,7 +44226,7 @@
       <x:c r="CT156" s="2"/>
       <x:c r="CU156" s="2"/>
       <x:c r="CV156" s="2"/>
-      <x:c r="CW156" s="2" t="str"/>
+      <x:c r="CW156" s="2"/>
       <x:c r="CX156" s="2"/>
       <x:c r="CY156" s="2"/>
       <x:c r="CZ156" s="2"/>
@@ -44159,13 +44431,13 @@
       <x:c r="AV157" s="2"/>
       <x:c r="AW157" s="2"/>
       <x:c r="AX157" s="2"/>
-      <x:c r="AY157" s="2" t="str">
+      <x:c r="AY157" s="2" t="str"/>
+      <x:c r="AZ157" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ157" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA157" s="2"/>
+      <x:c r="BA157" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB157" s="2"/>
       <x:c r="BC157" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -44181,7 +44453,9 @@
       <x:c r="BL157" s="2"/>
       <x:c r="BM157" s="2"/>
       <x:c r="BN157" s="2"/>
-      <x:c r="BO157" s="2"/>
+      <x:c r="BO157" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP157" s="2"/>
       <x:c r="BQ157" s="2"/>
       <x:c r="BR157" s="2" t="n">
@@ -44237,7 +44511,7 @@
       <x:c r="CT157" s="2"/>
       <x:c r="CU157" s="2"/>
       <x:c r="CV157" s="2"/>
-      <x:c r="CW157" s="2" t="str"/>
+      <x:c r="CW157" s="2"/>
       <x:c r="CX157" s="2"/>
       <x:c r="CY157" s="2"/>
       <x:c r="CZ157" s="2"/>
@@ -44442,13 +44716,13 @@
       <x:c r="AV158" s="2"/>
       <x:c r="AW158" s="2"/>
       <x:c r="AX158" s="2"/>
-      <x:c r="AY158" s="2" t="str">
+      <x:c r="AY158" s="2" t="str"/>
+      <x:c r="AZ158" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ158" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA158" s="2"/>
+      <x:c r="BA158" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB158" s="2"/>
       <x:c r="BC158" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -44464,7 +44738,9 @@
       <x:c r="BL158" s="2"/>
       <x:c r="BM158" s="2"/>
       <x:c r="BN158" s="2"/>
-      <x:c r="BO158" s="2"/>
+      <x:c r="BO158" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP158" s="2"/>
       <x:c r="BQ158" s="2"/>
       <x:c r="BR158" s="2" t="n">
@@ -44520,7 +44796,7 @@
       <x:c r="CT158" s="2"/>
       <x:c r="CU158" s="2"/>
       <x:c r="CV158" s="2"/>
-      <x:c r="CW158" s="2" t="str"/>
+      <x:c r="CW158" s="2"/>
       <x:c r="CX158" s="2"/>
       <x:c r="CY158" s="2"/>
       <x:c r="CZ158" s="2"/>
@@ -44725,13 +45001,13 @@
       <x:c r="AV159" s="2"/>
       <x:c r="AW159" s="2"/>
       <x:c r="AX159" s="2"/>
-      <x:c r="AY159" s="2" t="str">
+      <x:c r="AY159" s="2" t="str"/>
+      <x:c r="AZ159" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ159" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA159" s="2"/>
+      <x:c r="BA159" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB159" s="2"/>
       <x:c r="BC159" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -44747,7 +45023,9 @@
       <x:c r="BL159" s="2"/>
       <x:c r="BM159" s="2"/>
       <x:c r="BN159" s="2"/>
-      <x:c r="BO159" s="2"/>
+      <x:c r="BO159" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP159" s="2"/>
       <x:c r="BQ159" s="2"/>
       <x:c r="BR159" s="2" t="n">
@@ -44802,7 +45080,7 @@
       <x:c r="CT159" s="2"/>
       <x:c r="CU159" s="2"/>
       <x:c r="CV159" s="2"/>
-      <x:c r="CW159" s="2" t="str"/>
+      <x:c r="CW159" s="2"/>
       <x:c r="CX159" s="2"/>
       <x:c r="CY159" s="2"/>
       <x:c r="CZ159" s="2"/>
@@ -45007,13 +45285,13 @@
       <x:c r="AV160" s="2"/>
       <x:c r="AW160" s="2"/>
       <x:c r="AX160" s="2"/>
-      <x:c r="AY160" s="2" t="str">
+      <x:c r="AY160" s="2" t="str"/>
+      <x:c r="AZ160" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ160" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA160" s="2"/>
+      <x:c r="BA160" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB160" s="2"/>
       <x:c r="BC160" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -45029,7 +45307,9 @@
       <x:c r="BL160" s="2"/>
       <x:c r="BM160" s="2"/>
       <x:c r="BN160" s="2"/>
-      <x:c r="BO160" s="2"/>
+      <x:c r="BO160" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP160" s="2"/>
       <x:c r="BQ160" s="2"/>
       <x:c r="BR160" s="2" t="n">
@@ -45085,7 +45365,7 @@
       <x:c r="CT160" s="2"/>
       <x:c r="CU160" s="2"/>
       <x:c r="CV160" s="2"/>
-      <x:c r="CW160" s="2" t="str"/>
+      <x:c r="CW160" s="2"/>
       <x:c r="CX160" s="2"/>
       <x:c r="CY160" s="2"/>
       <x:c r="CZ160" s="2"/>
@@ -45290,13 +45570,13 @@
       <x:c r="AV161" s="2"/>
       <x:c r="AW161" s="2"/>
       <x:c r="AX161" s="2"/>
-      <x:c r="AY161" s="2" t="str">
+      <x:c r="AY161" s="2" t="str"/>
+      <x:c r="AZ161" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ161" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA161" s="2"/>
+      <x:c r="BA161" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB161" s="2"/>
       <x:c r="BC161" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -45312,7 +45592,9 @@
       <x:c r="BL161" s="2"/>
       <x:c r="BM161" s="2"/>
       <x:c r="BN161" s="2"/>
-      <x:c r="BO161" s="2"/>
+      <x:c r="BO161" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP161" s="2"/>
       <x:c r="BQ161" s="2"/>
       <x:c r="BR161" s="2" t="n">
@@ -45368,7 +45650,7 @@
       <x:c r="CT161" s="2"/>
       <x:c r="CU161" s="2"/>
       <x:c r="CV161" s="2"/>
-      <x:c r="CW161" s="2" t="str"/>
+      <x:c r="CW161" s="2"/>
       <x:c r="CX161" s="2"/>
       <x:c r="CY161" s="2"/>
       <x:c r="CZ161" s="2"/>
@@ -45820,13 +46102,13 @@
       <x:c r="AV163" s="2"/>
       <x:c r="AW163" s="2"/>
       <x:c r="AX163" s="2"/>
-      <x:c r="AY163" s="2" t="str">
+      <x:c r="AY163" s="2" t="str"/>
+      <x:c r="AZ163" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ163" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA163" s="2"/>
+      <x:c r="BA163" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB163" s="2"/>
       <x:c r="BC163" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -45842,7 +46124,9 @@
       <x:c r="BL163" s="2"/>
       <x:c r="BM163" s="2"/>
       <x:c r="BN163" s="2"/>
-      <x:c r="BO163" s="2"/>
+      <x:c r="BO163" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP163" s="2"/>
       <x:c r="BQ163" s="2"/>
       <x:c r="BR163" s="2" t="n">
@@ -45901,7 +46185,7 @@
       <x:c r="CT163" s="2"/>
       <x:c r="CU163" s="2"/>
       <x:c r="CV163" s="2"/>
-      <x:c r="CW163" s="2" t="str"/>
+      <x:c r="CW163" s="2"/>
       <x:c r="CX163" s="2"/>
       <x:c r="CY163" s="2"/>
       <x:c r="CZ163" s="2"/>
@@ -46106,13 +46390,13 @@
       <x:c r="AV164" s="2"/>
       <x:c r="AW164" s="2"/>
       <x:c r="AX164" s="2"/>
-      <x:c r="AY164" s="2" t="str">
+      <x:c r="AY164" s="2" t="str"/>
+      <x:c r="AZ164" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ164" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA164" s="2"/>
+      <x:c r="BA164" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB164" s="2"/>
       <x:c r="BC164" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -46128,7 +46412,9 @@
       <x:c r="BL164" s="2"/>
       <x:c r="BM164" s="2"/>
       <x:c r="BN164" s="2"/>
-      <x:c r="BO164" s="2"/>
+      <x:c r="BO164" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP164" s="2"/>
       <x:c r="BQ164" s="2"/>
       <x:c r="BR164" s="2" t="n">
@@ -46184,7 +46470,7 @@
       <x:c r="CT164" s="2"/>
       <x:c r="CU164" s="2"/>
       <x:c r="CV164" s="2"/>
-      <x:c r="CW164" s="2" t="str"/>
+      <x:c r="CW164" s="2"/>
       <x:c r="CX164" s="2"/>
       <x:c r="CY164" s="2"/>
       <x:c r="CZ164" s="2"/>
@@ -46389,13 +46675,13 @@
       <x:c r="AV165" s="2"/>
       <x:c r="AW165" s="2"/>
       <x:c r="AX165" s="2"/>
-      <x:c r="AY165" s="2" t="str">
+      <x:c r="AY165" s="2" t="str"/>
+      <x:c r="AZ165" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ165" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA165" s="2"/>
+      <x:c r="BA165" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB165" s="2"/>
       <x:c r="BC165" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -46411,7 +46697,9 @@
       <x:c r="BL165" s="2"/>
       <x:c r="BM165" s="2"/>
       <x:c r="BN165" s="2"/>
-      <x:c r="BO165" s="2"/>
+      <x:c r="BO165" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP165" s="2"/>
       <x:c r="BQ165" s="2"/>
       <x:c r="BR165" s="2" t="n">
@@ -46467,7 +46755,7 @@
       <x:c r="CT165" s="2"/>
       <x:c r="CU165" s="2"/>
       <x:c r="CV165" s="2"/>
-      <x:c r="CW165" s="2" t="str"/>
+      <x:c r="CW165" s="2"/>
       <x:c r="CX165" s="2"/>
       <x:c r="CY165" s="2"/>
       <x:c r="CZ165" s="2"/>
@@ -46672,13 +46960,13 @@
       <x:c r="AV166" s="2"/>
       <x:c r="AW166" s="2"/>
       <x:c r="AX166" s="2"/>
-      <x:c r="AY166" s="2" t="str">
+      <x:c r="AY166" s="2" t="str"/>
+      <x:c r="AZ166" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ166" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA166" s="2"/>
+      <x:c r="BA166" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB166" s="2"/>
       <x:c r="BC166" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -46694,7 +46982,9 @@
       <x:c r="BL166" s="2"/>
       <x:c r="BM166" s="2"/>
       <x:c r="BN166" s="2"/>
-      <x:c r="BO166" s="2"/>
+      <x:c r="BO166" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP166" s="2"/>
       <x:c r="BQ166" s="2"/>
       <x:c r="BR166" s="2" t="n">
@@ -46752,7 +47042,7 @@
       <x:c r="CT166" s="2"/>
       <x:c r="CU166" s="2"/>
       <x:c r="CV166" s="2"/>
-      <x:c r="CW166" s="2" t="str"/>
+      <x:c r="CW166" s="2"/>
       <x:c r="CX166" s="2"/>
       <x:c r="CY166" s="2"/>
       <x:c r="CZ166" s="2"/>
@@ -46957,13 +47247,13 @@
       <x:c r="AV167" s="2"/>
       <x:c r="AW167" s="2"/>
       <x:c r="AX167" s="2"/>
-      <x:c r="AY167" s="2" t="str">
+      <x:c r="AY167" s="2" t="str"/>
+      <x:c r="AZ167" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ167" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA167" s="2"/>
+      <x:c r="BA167" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB167" s="2"/>
       <x:c r="BC167" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -46979,7 +47269,9 @@
       <x:c r="BL167" s="2"/>
       <x:c r="BM167" s="2"/>
       <x:c r="BN167" s="2"/>
-      <x:c r="BO167" s="2"/>
+      <x:c r="BO167" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP167" s="2"/>
       <x:c r="BQ167" s="2"/>
       <x:c r="BR167" s="2" t="n">
@@ -47036,7 +47328,7 @@
       <x:c r="CT167" s="2"/>
       <x:c r="CU167" s="2"/>
       <x:c r="CV167" s="2"/>
-      <x:c r="CW167" s="2" t="str"/>
+      <x:c r="CW167" s="2"/>
       <x:c r="CX167" s="2"/>
       <x:c r="CY167" s="2"/>
       <x:c r="CZ167" s="2"/>
@@ -47241,13 +47533,13 @@
       <x:c r="AV168" s="2"/>
       <x:c r="AW168" s="2"/>
       <x:c r="AX168" s="2"/>
-      <x:c r="AY168" s="2" t="str">
+      <x:c r="AY168" s="2" t="str"/>
+      <x:c r="AZ168" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ168" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA168" s="2"/>
+      <x:c r="BA168" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB168" s="2"/>
       <x:c r="BC168" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -47263,7 +47555,9 @@
       <x:c r="BL168" s="2"/>
       <x:c r="BM168" s="2"/>
       <x:c r="BN168" s="2"/>
-      <x:c r="BO168" s="2"/>
+      <x:c r="BO168" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP168" s="2"/>
       <x:c r="BQ168" s="2"/>
       <x:c r="BR168" s="2" t="n">
@@ -47319,7 +47613,7 @@
       <x:c r="CT168" s="2"/>
       <x:c r="CU168" s="2"/>
       <x:c r="CV168" s="2"/>
-      <x:c r="CW168" s="2" t="str"/>
+      <x:c r="CW168" s="2"/>
       <x:c r="CX168" s="2"/>
       <x:c r="CY168" s="2"/>
       <x:c r="CZ168" s="2"/>
@@ -47524,13 +47818,13 @@
       <x:c r="AV169" s="2"/>
       <x:c r="AW169" s="2"/>
       <x:c r="AX169" s="2"/>
-      <x:c r="AY169" s="2" t="str">
+      <x:c r="AY169" s="2" t="str"/>
+      <x:c r="AZ169" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ169" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA169" s="2"/>
+      <x:c r="BA169" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB169" s="2"/>
       <x:c r="BC169" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -47546,7 +47840,9 @@
       <x:c r="BL169" s="2"/>
       <x:c r="BM169" s="2"/>
       <x:c r="BN169" s="2"/>
-      <x:c r="BO169" s="2"/>
+      <x:c r="BO169" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP169" s="2"/>
       <x:c r="BQ169" s="2"/>
       <x:c r="BR169" s="2" t="n">
@@ -47602,7 +47898,7 @@
       <x:c r="CT169" s="2"/>
       <x:c r="CU169" s="2"/>
       <x:c r="CV169" s="2"/>
-      <x:c r="CW169" s="2" t="str"/>
+      <x:c r="CW169" s="2"/>
       <x:c r="CX169" s="2"/>
       <x:c r="CY169" s="2"/>
       <x:c r="CZ169" s="2"/>
@@ -47807,13 +48103,13 @@
       <x:c r="AV170" s="2"/>
       <x:c r="AW170" s="2"/>
       <x:c r="AX170" s="2"/>
-      <x:c r="AY170" s="2" t="str">
+      <x:c r="AY170" s="2" t="str"/>
+      <x:c r="AZ170" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ170" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA170" s="2"/>
+      <x:c r="BA170" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB170" s="2"/>
       <x:c r="BC170" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -47829,7 +48125,9 @@
       <x:c r="BL170" s="2"/>
       <x:c r="BM170" s="2"/>
       <x:c r="BN170" s="2"/>
-      <x:c r="BO170" s="2"/>
+      <x:c r="BO170" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP170" s="2"/>
       <x:c r="BQ170" s="2"/>
       <x:c r="BR170" s="2" t="n">
@@ -47885,7 +48183,7 @@
       <x:c r="CT170" s="2"/>
       <x:c r="CU170" s="2"/>
       <x:c r="CV170" s="2"/>
-      <x:c r="CW170" s="2" t="str"/>
+      <x:c r="CW170" s="2"/>
       <x:c r="CX170" s="2"/>
       <x:c r="CY170" s="2"/>
       <x:c r="CZ170" s="2"/>
@@ -48337,13 +48635,13 @@
       <x:c r="AV172" s="2"/>
       <x:c r="AW172" s="2"/>
       <x:c r="AX172" s="2"/>
-      <x:c r="AY172" s="2" t="str">
+      <x:c r="AY172" s="2" t="str"/>
+      <x:c r="AZ172" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ172" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA172" s="2"/>
+      <x:c r="BA172" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB172" s="2"/>
       <x:c r="BC172" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -48359,7 +48657,9 @@
       <x:c r="BL172" s="2"/>
       <x:c r="BM172" s="2"/>
       <x:c r="BN172" s="2"/>
-      <x:c r="BO172" s="2"/>
+      <x:c r="BO172" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP172" s="2"/>
       <x:c r="BQ172" s="2"/>
       <x:c r="BR172" s="2" t="n">
@@ -48415,7 +48715,7 @@
       <x:c r="CT172" s="2"/>
       <x:c r="CU172" s="2"/>
       <x:c r="CV172" s="2"/>
-      <x:c r="CW172" s="2" t="str"/>
+      <x:c r="CW172" s="2"/>
       <x:c r="CX172" s="2"/>
       <x:c r="CY172" s="2"/>
       <x:c r="CZ172" s="2"/>
@@ -48620,13 +48920,13 @@
       <x:c r="AV173" s="2"/>
       <x:c r="AW173" s="2"/>
       <x:c r="AX173" s="2"/>
-      <x:c r="AY173" s="2" t="str">
+      <x:c r="AY173" s="2" t="str"/>
+      <x:c r="AZ173" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ173" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA173" s="2"/>
+      <x:c r="BA173" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB173" s="2"/>
       <x:c r="BC173" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -48642,7 +48942,9 @@
       <x:c r="BL173" s="2"/>
       <x:c r="BM173" s="2"/>
       <x:c r="BN173" s="2"/>
-      <x:c r="BO173" s="2"/>
+      <x:c r="BO173" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP173" s="2"/>
       <x:c r="BQ173" s="2"/>
       <x:c r="BR173" s="2" t="n">
@@ -48697,7 +48999,7 @@
       <x:c r="CT173" s="2"/>
       <x:c r="CU173" s="2"/>
       <x:c r="CV173" s="2"/>
-      <x:c r="CW173" s="2" t="str"/>
+      <x:c r="CW173" s="2"/>
       <x:c r="CX173" s="2"/>
       <x:c r="CY173" s="2"/>
       <x:c r="CZ173" s="2"/>
@@ -48902,13 +49204,13 @@
       <x:c r="AV174" s="2"/>
       <x:c r="AW174" s="2"/>
       <x:c r="AX174" s="2"/>
-      <x:c r="AY174" s="2" t="str">
+      <x:c r="AY174" s="2" t="str"/>
+      <x:c r="AZ174" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ174" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA174" s="2"/>
+      <x:c r="BA174" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB174" s="2"/>
       <x:c r="BC174" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -48924,7 +49226,9 @@
       <x:c r="BL174" s="2"/>
       <x:c r="BM174" s="2"/>
       <x:c r="BN174" s="2"/>
-      <x:c r="BO174" s="2"/>
+      <x:c r="BO174" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP174" s="2"/>
       <x:c r="BQ174" s="2"/>
       <x:c r="BR174" s="2" t="n">
@@ -48979,7 +49283,7 @@
       <x:c r="CT174" s="2"/>
       <x:c r="CU174" s="2"/>
       <x:c r="CV174" s="2"/>
-      <x:c r="CW174" s="2" t="str"/>
+      <x:c r="CW174" s="2"/>
       <x:c r="CX174" s="2"/>
       <x:c r="CY174" s="2"/>
       <x:c r="CZ174" s="2"/>
@@ -49184,13 +49488,13 @@
       <x:c r="AV175" s="2"/>
       <x:c r="AW175" s="2"/>
       <x:c r="AX175" s="2"/>
-      <x:c r="AY175" s="2" t="str">
+      <x:c r="AY175" s="2" t="str"/>
+      <x:c r="AZ175" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ175" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA175" s="2"/>
+      <x:c r="BA175" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB175" s="2"/>
       <x:c r="BC175" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -49206,7 +49510,9 @@
       <x:c r="BL175" s="2"/>
       <x:c r="BM175" s="2"/>
       <x:c r="BN175" s="2"/>
-      <x:c r="BO175" s="2"/>
+      <x:c r="BO175" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP175" s="2"/>
       <x:c r="BQ175" s="2"/>
       <x:c r="BR175" s="2" t="n">
@@ -49262,7 +49568,7 @@
       <x:c r="CT175" s="2"/>
       <x:c r="CU175" s="2"/>
       <x:c r="CV175" s="2"/>
-      <x:c r="CW175" s="2" t="str"/>
+      <x:c r="CW175" s="2"/>
       <x:c r="CX175" s="2"/>
       <x:c r="CY175" s="2"/>
       <x:c r="CZ175" s="2"/>
@@ -49467,13 +49773,13 @@
       <x:c r="AV176" s="2"/>
       <x:c r="AW176" s="2"/>
       <x:c r="AX176" s="2"/>
-      <x:c r="AY176" s="2" t="str">
+      <x:c r="AY176" s="2" t="str"/>
+      <x:c r="AZ176" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ176" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA176" s="2"/>
+      <x:c r="BA176" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB176" s="2"/>
       <x:c r="BC176" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -49489,7 +49795,9 @@
       <x:c r="BL176" s="2"/>
       <x:c r="BM176" s="2"/>
       <x:c r="BN176" s="2"/>
-      <x:c r="BO176" s="2"/>
+      <x:c r="BO176" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP176" s="2"/>
       <x:c r="BQ176" s="2"/>
       <x:c r="BR176" s="2" t="n">
@@ -49545,7 +49853,7 @@
       <x:c r="CT176" s="2"/>
       <x:c r="CU176" s="2"/>
       <x:c r="CV176" s="2"/>
-      <x:c r="CW176" s="2" t="str"/>
+      <x:c r="CW176" s="2"/>
       <x:c r="CX176" s="2"/>
       <x:c r="CY176" s="2"/>
       <x:c r="CZ176" s="2"/>
@@ -50244,13 +50552,13 @@
       <x:c r="AV179" s="2"/>
       <x:c r="AW179" s="2"/>
       <x:c r="AX179" s="2"/>
-      <x:c r="AY179" s="2" t="str">
+      <x:c r="AY179" s="2" t="str"/>
+      <x:c r="AZ179" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ179" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA179" s="2"/>
+      <x:c r="BA179" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB179" s="2"/>
       <x:c r="BC179" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -50266,7 +50574,9 @@
       <x:c r="BL179" s="2"/>
       <x:c r="BM179" s="2"/>
       <x:c r="BN179" s="2"/>
-      <x:c r="BO179" s="2"/>
+      <x:c r="BO179" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP179" s="2"/>
       <x:c r="BQ179" s="2"/>
       <x:c r="BR179" s="2" t="n">
@@ -50320,7 +50630,7 @@
       <x:c r="CT179" s="2"/>
       <x:c r="CU179" s="2"/>
       <x:c r="CV179" s="2"/>
-      <x:c r="CW179" s="2" t="str"/>
+      <x:c r="CW179" s="2"/>
       <x:c r="CX179" s="2"/>
       <x:c r="CY179" s="2"/>
       <x:c r="CZ179" s="2"/>
@@ -50525,13 +50835,13 @@
       <x:c r="AV180" s="2"/>
       <x:c r="AW180" s="2"/>
       <x:c r="AX180" s="2"/>
-      <x:c r="AY180" s="2" t="str">
+      <x:c r="AY180" s="2" t="str"/>
+      <x:c r="AZ180" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ180" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA180" s="2"/>
+      <x:c r="BA180" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB180" s="2"/>
       <x:c r="BC180" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -50547,7 +50857,9 @@
       <x:c r="BL180" s="2"/>
       <x:c r="BM180" s="2"/>
       <x:c r="BN180" s="2"/>
-      <x:c r="BO180" s="2"/>
+      <x:c r="BO180" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP180" s="2"/>
       <x:c r="BQ180" s="2"/>
       <x:c r="BR180" s="2" t="n">
@@ -50602,7 +50914,7 @@
       <x:c r="CT180" s="2"/>
       <x:c r="CU180" s="2"/>
       <x:c r="CV180" s="2"/>
-      <x:c r="CW180" s="2" t="str"/>
+      <x:c r="CW180" s="2"/>
       <x:c r="CX180" s="2"/>
       <x:c r="CY180" s="2"/>
       <x:c r="CZ180" s="2"/>
@@ -50807,13 +51119,13 @@
       <x:c r="AV181" s="2"/>
       <x:c r="AW181" s="2"/>
       <x:c r="AX181" s="2"/>
-      <x:c r="AY181" s="2" t="str">
+      <x:c r="AY181" s="2" t="str"/>
+      <x:c r="AZ181" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ181" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA181" s="2"/>
+      <x:c r="BA181" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB181" s="2"/>
       <x:c r="BC181" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -50829,7 +51141,9 @@
       <x:c r="BL181" s="2"/>
       <x:c r="BM181" s="2"/>
       <x:c r="BN181" s="2"/>
-      <x:c r="BO181" s="2"/>
+      <x:c r="BO181" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP181" s="2"/>
       <x:c r="BQ181" s="2"/>
       <x:c r="BR181" s="2" t="n">
@@ -50883,7 +51197,7 @@
       <x:c r="CT181" s="2"/>
       <x:c r="CU181" s="2"/>
       <x:c r="CV181" s="2"/>
-      <x:c r="CW181" s="2" t="str"/>
+      <x:c r="CW181" s="2"/>
       <x:c r="CX181" s="2"/>
       <x:c r="CY181" s="2"/>
       <x:c r="CZ181" s="2"/>
@@ -51088,13 +51402,13 @@
       <x:c r="AV182" s="2"/>
       <x:c r="AW182" s="2"/>
       <x:c r="AX182" s="2"/>
-      <x:c r="AY182" s="2" t="str">
+      <x:c r="AY182" s="2" t="str"/>
+      <x:c r="AZ182" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ182" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA182" s="2"/>
+      <x:c r="BA182" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB182" s="2"/>
       <x:c r="BC182" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -51110,7 +51424,9 @@
       <x:c r="BL182" s="2"/>
       <x:c r="BM182" s="2"/>
       <x:c r="BN182" s="2"/>
-      <x:c r="BO182" s="2"/>
+      <x:c r="BO182" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP182" s="2"/>
       <x:c r="BQ182" s="2"/>
       <x:c r="BR182" s="2" t="n">
@@ -51164,7 +51480,7 @@
       <x:c r="CT182" s="2"/>
       <x:c r="CU182" s="2"/>
       <x:c r="CV182" s="2"/>
-      <x:c r="CW182" s="2" t="str"/>
+      <x:c r="CW182" s="2"/>
       <x:c r="CX182" s="2"/>
       <x:c r="CY182" s="2"/>
       <x:c r="CZ182" s="2"/>
@@ -51369,13 +51685,13 @@
       <x:c r="AV183" s="2"/>
       <x:c r="AW183" s="2"/>
       <x:c r="AX183" s="2"/>
-      <x:c r="AY183" s="2" t="str">
+      <x:c r="AY183" s="2" t="str"/>
+      <x:c r="AZ183" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ183" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA183" s="2"/>
+      <x:c r="BA183" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB183" s="2"/>
       <x:c r="BC183" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -51391,7 +51707,9 @@
       <x:c r="BL183" s="2"/>
       <x:c r="BM183" s="2"/>
       <x:c r="BN183" s="2"/>
-      <x:c r="BO183" s="2"/>
+      <x:c r="BO183" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP183" s="2"/>
       <x:c r="BQ183" s="2"/>
       <x:c r="BR183" s="2" t="n">
@@ -51446,7 +51764,7 @@
       <x:c r="CT183" s="2"/>
       <x:c r="CU183" s="2"/>
       <x:c r="CV183" s="2"/>
-      <x:c r="CW183" s="2" t="str"/>
+      <x:c r="CW183" s="2"/>
       <x:c r="CX183" s="2"/>
       <x:c r="CY183" s="2"/>
       <x:c r="CZ183" s="2"/>
@@ -51651,13 +51969,13 @@
       <x:c r="AV184" s="2"/>
       <x:c r="AW184" s="2"/>
       <x:c r="AX184" s="2"/>
-      <x:c r="AY184" s="2" t="str">
+      <x:c r="AY184" s="2" t="str"/>
+      <x:c r="AZ184" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ184" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA184" s="2"/>
+      <x:c r="BA184" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB184" s="2"/>
       <x:c r="BC184" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -51673,7 +51991,9 @@
       <x:c r="BL184" s="2"/>
       <x:c r="BM184" s="2"/>
       <x:c r="BN184" s="2"/>
-      <x:c r="BO184" s="2"/>
+      <x:c r="BO184" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP184" s="2"/>
       <x:c r="BQ184" s="2"/>
       <x:c r="BR184" s="2" t="n">
@@ -51728,7 +52048,7 @@
       <x:c r="CT184" s="2"/>
       <x:c r="CU184" s="2"/>
       <x:c r="CV184" s="2"/>
-      <x:c r="CW184" s="2" t="str"/>
+      <x:c r="CW184" s="2"/>
       <x:c r="CX184" s="2"/>
       <x:c r="CY184" s="2"/>
       <x:c r="CZ184" s="2"/>
@@ -51933,13 +52253,13 @@
       <x:c r="AV185" s="2"/>
       <x:c r="AW185" s="2"/>
       <x:c r="AX185" s="2"/>
-      <x:c r="AY185" s="2" t="str">
+      <x:c r="AY185" s="2" t="str"/>
+      <x:c r="AZ185" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ185" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA185" s="2"/>
+      <x:c r="BA185" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB185" s="2"/>
       <x:c r="BC185" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -51955,7 +52275,9 @@
       <x:c r="BL185" s="2"/>
       <x:c r="BM185" s="2"/>
       <x:c r="BN185" s="2"/>
-      <x:c r="BO185" s="2"/>
+      <x:c r="BO185" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP185" s="2"/>
       <x:c r="BQ185" s="2"/>
       <x:c r="BR185" s="2" t="n">
@@ -52009,7 +52331,7 @@
       <x:c r="CT185" s="2"/>
       <x:c r="CU185" s="2"/>
       <x:c r="CV185" s="2"/>
-      <x:c r="CW185" s="2" t="str"/>
+      <x:c r="CW185" s="2"/>
       <x:c r="CX185" s="2"/>
       <x:c r="CY185" s="2"/>
       <x:c r="CZ185" s="2"/>
@@ -52461,13 +52783,13 @@
       <x:c r="AV187" s="2"/>
       <x:c r="AW187" s="2"/>
       <x:c r="AX187" s="2"/>
-      <x:c r="AY187" s="2" t="str">
+      <x:c r="AY187" s="2" t="str"/>
+      <x:c r="AZ187" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ187" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA187" s="2"/>
+      <x:c r="BA187" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB187" s="2"/>
       <x:c r="BC187" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -52483,7 +52805,9 @@
       <x:c r="BL187" s="2"/>
       <x:c r="BM187" s="2"/>
       <x:c r="BN187" s="2"/>
-      <x:c r="BO187" s="2"/>
+      <x:c r="BO187" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP187" s="2"/>
       <x:c r="BQ187" s="2"/>
       <x:c r="BR187" s="2" t="n">
@@ -52537,7 +52861,7 @@
       <x:c r="CT187" s="2"/>
       <x:c r="CU187" s="2"/>
       <x:c r="CV187" s="2"/>
-      <x:c r="CW187" s="2" t="str"/>
+      <x:c r="CW187" s="2"/>
       <x:c r="CX187" s="2"/>
       <x:c r="CY187" s="2"/>
       <x:c r="CZ187" s="2"/>
@@ -52742,13 +53066,13 @@
       <x:c r="AV188" s="2"/>
       <x:c r="AW188" s="2"/>
       <x:c r="AX188" s="2"/>
-      <x:c r="AY188" s="2" t="str">
+      <x:c r="AY188" s="2" t="str"/>
+      <x:c r="AZ188" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ188" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA188" s="2"/>
+      <x:c r="BA188" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB188" s="2"/>
       <x:c r="BC188" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -52764,7 +53088,9 @@
       <x:c r="BL188" s="2"/>
       <x:c r="BM188" s="2"/>
       <x:c r="BN188" s="2"/>
-      <x:c r="BO188" s="2"/>
+      <x:c r="BO188" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP188" s="2"/>
       <x:c r="BQ188" s="2"/>
       <x:c r="BR188" s="2" t="n">
@@ -52817,7 +53143,7 @@
       <x:c r="CT188" s="2"/>
       <x:c r="CU188" s="2"/>
       <x:c r="CV188" s="2"/>
-      <x:c r="CW188" s="2" t="str"/>
+      <x:c r="CW188" s="2"/>
       <x:c r="CX188" s="2"/>
       <x:c r="CY188" s="2"/>
       <x:c r="CZ188" s="2"/>
@@ -53022,13 +53348,13 @@
       <x:c r="AV189" s="2"/>
       <x:c r="AW189" s="2"/>
       <x:c r="AX189" s="2"/>
-      <x:c r="AY189" s="2" t="str">
+      <x:c r="AY189" s="2" t="str"/>
+      <x:c r="AZ189" s="2" t="str">
         <x:v>init</x:v>
       </x:c>
-      <x:c r="AZ189" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BA189" s="2"/>
+      <x:c r="BA189" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BB189" s="2"/>
       <x:c r="BC189" s="2" t="str">
         <x:v>迭代内（TR4A前）</x:v>
@@ -53044,7 +53370,9 @@
       <x:c r="BL189" s="2"/>
       <x:c r="BM189" s="2"/>
       <x:c r="BN189" s="2"/>
-      <x:c r="BO189" s="2"/>
+      <x:c r="BO189" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="BP189" s="2"/>
       <x:c r="BQ189" s="2"/>
       <x:c r="BR189" s="2" t="n">
@@ -53098,7 +53426,7 @@
       <x:c r="CT189" s="2"/>
       <x:c r="CU189" s="2"/>
       <x:c r="CV189" s="2"/>
-      <x:c r="CW189" s="2" t="str"/>
+      <x:c r="CW189" s="2"/>
       <x:c r="CX189" s="2"/>
       <x:c r="CY189" s="2"/>
       <x:c r="CZ189" s="2"/>
